--- a/review-results/河北实时运行及市场出清数据-20260907.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260907.xlsx
@@ -4288,17 +4288,39 @@
       <s:c r="E2" s="1" t="n">
         <s:v>403.44</s:v>
       </s:c>
-      <s:c r="F2" s="1"/>
-      <s:c r="G2" s="1"/>
-      <s:c r="H2" s="1"/>
-      <s:c r="I2" s="1"/>
-      <s:c r="J2" s="1"/>
-      <s:c r="K2" s="1"/>
-      <s:c r="L2" s="1"/>
-      <s:c r="M2" s="1"/>
-      <s:c r="N2" s="1"/>
-      <s:c r="O2" s="1"/>
-      <s:c r="P2" s="1"/>
+      <s:c r="F2" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G2" s="1" t="n">
+        <s:v>2293.15</s:v>
+      </s:c>
+      <s:c r="H2" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I2" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L2" s="1" t="n">
+        <s:v>360.13</s:v>
+      </s:c>
+      <s:c r="M2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N2" s="1" t="n">
+        <s:v>20711.42</s:v>
+      </s:c>
+      <s:c r="O2" s="1" t="n">
+        <s:v>1198.7</s:v>
+      </s:c>
+      <s:c r="P2" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="3" s="1" customFormat="1" spans="1:16">
       <s:c r="A3" s="6" t="n">
@@ -4314,17 +4336,39 @@
       <s:c r="E3" s="1" t="n">
         <s:v>406.89</s:v>
       </s:c>
-      <s:c r="F3" s="1"/>
-      <s:c r="G3" s="1"/>
-      <s:c r="H3" s="1"/>
-      <s:c r="I3" s="1"/>
-      <s:c r="J3" s="1"/>
-      <s:c r="K3" s="1"/>
-      <s:c r="L3" s="1"/>
-      <s:c r="M3" s="1"/>
-      <s:c r="N3" s="1"/>
-      <s:c r="O3" s="1"/>
-      <s:c r="P3" s="1"/>
+      <s:c r="F3" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G3" s="1" t="n">
+        <s:v>2289.04</s:v>
+      </s:c>
+      <s:c r="H3" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I3" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J3" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K3" s="1" t="n">
+        <s:v>302.2</s:v>
+      </s:c>
+      <s:c r="L3" s="1" t="n">
+        <s:v>356.95</s:v>
+      </s:c>
+      <s:c r="M3" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N3" s="1" t="n">
+        <s:v>21136.31</s:v>
+      </s:c>
+      <s:c r="O3" s="1" t="n">
+        <s:v>1210.01</s:v>
+      </s:c>
+      <s:c r="P3" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="4" s="1" customFormat="1" spans="1:16">
       <s:c r="A4" s="6" t="n">
@@ -4340,17 +4384,39 @@
       <s:c r="E4" s="1" t="n">
         <s:v>403.44</s:v>
       </s:c>
-      <s:c r="F4" s="1"/>
-      <s:c r="G4" s="1"/>
-      <s:c r="H4" s="1"/>
-      <s:c r="I4" s="1"/>
-      <s:c r="J4" s="1"/>
-      <s:c r="K4" s="1"/>
-      <s:c r="L4" s="1"/>
-      <s:c r="M4" s="1"/>
-      <s:c r="N4" s="1"/>
-      <s:c r="O4" s="1"/>
-      <s:c r="P4" s="1"/>
+      <s:c r="F4" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G4" s="1" t="n">
+        <s:v>2273.36</s:v>
+      </s:c>
+      <s:c r="H4" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I4" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J4" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K4" s="1" t="n">
+        <s:v>299</s:v>
+      </s:c>
+      <s:c r="L4" s="1" t="n">
+        <s:v>357.9</s:v>
+      </s:c>
+      <s:c r="M4" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N4" s="1" t="n">
+        <s:v>20850.65</s:v>
+      </s:c>
+      <s:c r="O4" s="1" t="n">
+        <s:v>1131.19</s:v>
+      </s:c>
+      <s:c r="P4" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="5" s="1" customFormat="1" spans="1:16">
       <s:c r="A5" s="6" t="n">
@@ -4366,17 +4432,39 @@
       <s:c r="E5" s="1" t="n">
         <s:v>401.36</s:v>
       </s:c>
-      <s:c r="F5" s="1"/>
-      <s:c r="G5" s="1"/>
-      <s:c r="H5" s="1"/>
-      <s:c r="I5" s="1"/>
-      <s:c r="J5" s="1"/>
-      <s:c r="K5" s="1"/>
-      <s:c r="L5" s="1"/>
-      <s:c r="M5" s="1"/>
-      <s:c r="N5" s="1"/>
-      <s:c r="O5" s="1"/>
-      <s:c r="P5" s="1"/>
+      <s:c r="F5" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G5" s="1" t="n">
+        <s:v>2276.96</s:v>
+      </s:c>
+      <s:c r="H5" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I5" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J5" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K5" s="1" t="n">
+        <s:v>301.1</s:v>
+      </s:c>
+      <s:c r="L5" s="1" t="n">
+        <s:v>356.96</s:v>
+      </s:c>
+      <s:c r="M5" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N5" s="1" t="n">
+        <s:v>20593.51</s:v>
+      </s:c>
+      <s:c r="O5" s="1" t="n">
+        <s:v>1120.38</s:v>
+      </s:c>
+      <s:c r="P5" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="6" s="1" customFormat="1" spans="1:16">
       <s:c r="A6" s="6" t="n">
@@ -4392,17 +4480,39 @@
       <s:c r="E6" s="1" t="n">
         <s:v>403.54</s:v>
       </s:c>
-      <s:c r="F6" s="1"/>
-      <s:c r="G6" s="1"/>
-      <s:c r="H6" s="1"/>
-      <s:c r="I6" s="1"/>
-      <s:c r="J6" s="1"/>
-      <s:c r="K6" s="1"/>
-      <s:c r="L6" s="1"/>
-      <s:c r="M6" s="1"/>
-      <s:c r="N6" s="1"/>
-      <s:c r="O6" s="1"/>
-      <s:c r="P6" s="1"/>
+      <s:c r="F6" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G6" s="1" t="n">
+        <s:v>2277.45</s:v>
+      </s:c>
+      <s:c r="H6" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I6" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J6" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K6" s="1" t="n">
+        <s:v>302.7</s:v>
+      </s:c>
+      <s:c r="L6" s="1" t="n">
+        <s:v>356.96</s:v>
+      </s:c>
+      <s:c r="M6" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N6" s="1" t="n">
+        <s:v>20939.07</s:v>
+      </s:c>
+      <s:c r="O6" s="1" t="n">
+        <s:v>1048.83</s:v>
+      </s:c>
+      <s:c r="P6" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="7" s="1" customFormat="1" spans="1:16">
       <s:c r="A7" s="6" t="n">
@@ -4418,17 +4528,39 @@
       <s:c r="E7" s="1" t="n">
         <s:v>398.8</s:v>
       </s:c>
-      <s:c r="F7" s="1"/>
-      <s:c r="G7" s="1"/>
-      <s:c r="H7" s="1"/>
-      <s:c r="I7" s="1"/>
-      <s:c r="J7" s="1"/>
-      <s:c r="K7" s="1"/>
-      <s:c r="L7" s="1"/>
-      <s:c r="M7" s="1"/>
-      <s:c r="N7" s="1"/>
-      <s:c r="O7" s="1"/>
-      <s:c r="P7" s="1"/>
+      <s:c r="F7" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G7" s="1" t="n">
+        <s:v>2289.28</s:v>
+      </s:c>
+      <s:c r="H7" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I7" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J7" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K7" s="1" t="n">
+        <s:v>298.8</s:v>
+      </s:c>
+      <s:c r="L7" s="1" t="n">
+        <s:v>356.64</s:v>
+      </s:c>
+      <s:c r="M7" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N7" s="1" t="n">
+        <s:v>20324.52</s:v>
+      </s:c>
+      <s:c r="O7" s="1" t="n">
+        <s:v>962.67</s:v>
+      </s:c>
+      <s:c r="P7" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="8" s="1" customFormat="1" spans="1:16">
       <s:c r="A8" s="6" t="n">
@@ -4444,17 +4576,39 @@
       <s:c r="E8" s="1" t="n">
         <s:v>398.54</s:v>
       </s:c>
-      <s:c r="F8" s="1"/>
-      <s:c r="G8" s="1"/>
-      <s:c r="H8" s="1"/>
-      <s:c r="I8" s="1"/>
-      <s:c r="J8" s="1"/>
-      <s:c r="K8" s="1"/>
-      <s:c r="L8" s="1"/>
-      <s:c r="M8" s="1"/>
-      <s:c r="N8" s="1"/>
-      <s:c r="O8" s="1"/>
-      <s:c r="P8" s="1"/>
+      <s:c r="F8" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G8" s="1" t="n">
+        <s:v>2252.5</s:v>
+      </s:c>
+      <s:c r="H8" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I8" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J8" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K8" s="1" t="n">
+        <s:v>299.1</s:v>
+      </s:c>
+      <s:c r="L8" s="1" t="n">
+        <s:v>356.96</s:v>
+      </s:c>
+      <s:c r="M8" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N8" s="1" t="n">
+        <s:v>19870.29</s:v>
+      </s:c>
+      <s:c r="O8" s="1" t="n">
+        <s:v>939.96</s:v>
+      </s:c>
+      <s:c r="P8" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="9" s="1" customFormat="1" spans="1:16">
       <s:c r="A9" s="6" t="n">
@@ -4470,17 +4624,39 @@
       <s:c r="E9" s="1" t="n">
         <s:v>398.94</s:v>
       </s:c>
-      <s:c r="F9" s="1"/>
-      <s:c r="G9" s="1"/>
-      <s:c r="H9" s="1"/>
-      <s:c r="I9" s="1"/>
-      <s:c r="J9" s="1"/>
-      <s:c r="K9" s="1"/>
-      <s:c r="L9" s="1"/>
-      <s:c r="M9" s="1"/>
-      <s:c r="N9" s="1"/>
-      <s:c r="O9" s="1"/>
-      <s:c r="P9" s="1"/>
+      <s:c r="F9" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G9" s="1" t="n">
+        <s:v>2263.95</s:v>
+      </s:c>
+      <s:c r="H9" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I9" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J9" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K9" s="1" t="n">
+        <s:v>300.3</s:v>
+      </s:c>
+      <s:c r="L9" s="1" t="n">
+        <s:v>356.5</s:v>
+      </s:c>
+      <s:c r="M9" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N9" s="1" t="n">
+        <s:v>19819.94</s:v>
+      </s:c>
+      <s:c r="O9" s="1" t="n">
+        <s:v>898.82</s:v>
+      </s:c>
+      <s:c r="P9" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="10" s="1" customFormat="1" spans="1:16">
       <s:c r="A10" s="6" t="n">
@@ -4496,17 +4672,39 @@
       <s:c r="E10" s="1" t="n">
         <s:v>404.32</s:v>
       </s:c>
-      <s:c r="F10" s="1"/>
-      <s:c r="G10" s="1"/>
-      <s:c r="H10" s="1"/>
-      <s:c r="I10" s="1"/>
-      <s:c r="J10" s="1"/>
-      <s:c r="K10" s="1"/>
-      <s:c r="L10" s="1"/>
-      <s:c r="M10" s="1"/>
-      <s:c r="N10" s="1"/>
-      <s:c r="O10" s="1"/>
-      <s:c r="P10" s="1"/>
+      <s:c r="F10" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G10" s="1" t="n">
+        <s:v>2246.15</s:v>
+      </s:c>
+      <s:c r="H10" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I10" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J10" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K10" s="1" t="n">
+        <s:v>539.8</s:v>
+      </s:c>
+      <s:c r="L10" s="1" t="n">
+        <s:v>356.18</s:v>
+      </s:c>
+      <s:c r="M10" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N10" s="1" t="n">
+        <s:v>21031.9</s:v>
+      </s:c>
+      <s:c r="O10" s="1" t="n">
+        <s:v>811.18</s:v>
+      </s:c>
+      <s:c r="P10" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="11" s="1" customFormat="1" spans="1:16">
       <s:c r="A11" s="6" t="n">
@@ -4522,17 +4720,39 @@
       <s:c r="E11" s="1" t="n">
         <s:v>1192</s:v>
       </s:c>
-      <s:c r="F11" s="1"/>
-      <s:c r="G11" s="1"/>
-      <s:c r="H11" s="1"/>
-      <s:c r="I11" s="1"/>
-      <s:c r="J11" s="1"/>
-      <s:c r="K11" s="1"/>
-      <s:c r="L11" s="1"/>
-      <s:c r="M11" s="1"/>
-      <s:c r="N11" s="1"/>
-      <s:c r="O11" s="1"/>
-      <s:c r="P11" s="1"/>
+      <s:c r="F11" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G11" s="1" t="n">
+        <s:v>2220.89</s:v>
+      </s:c>
+      <s:c r="H11" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I11" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J11" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K11" s="1" t="n">
+        <s:v>852.3</s:v>
+      </s:c>
+      <s:c r="L11" s="1" t="n">
+        <s:v>357.46</s:v>
+      </s:c>
+      <s:c r="M11" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N11" s="1" t="n">
+        <s:v>21886.34</s:v>
+      </s:c>
+      <s:c r="O11" s="1" t="n">
+        <s:v>743.11</s:v>
+      </s:c>
+      <s:c r="P11" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="12" s="1" customFormat="1" spans="1:16">
       <s:c r="A12" s="6" t="n">
@@ -4548,17 +4768,39 @@
       <s:c r="E12" s="1" t="n">
         <s:v>407.73</s:v>
       </s:c>
-      <s:c r="F12" s="1"/>
-      <s:c r="G12" s="1"/>
-      <s:c r="H12" s="1"/>
-      <s:c r="I12" s="1"/>
-      <s:c r="J12" s="1"/>
-      <s:c r="K12" s="1"/>
-      <s:c r="L12" s="1"/>
-      <s:c r="M12" s="1"/>
-      <s:c r="N12" s="1"/>
-      <s:c r="O12" s="1"/>
-      <s:c r="P12" s="1"/>
+      <s:c r="F12" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G12" s="1" t="n">
+        <s:v>2180.33</s:v>
+      </s:c>
+      <s:c r="H12" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I12" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J12" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K12" s="1" t="n">
+        <s:v>851.3</s:v>
+      </s:c>
+      <s:c r="L12" s="1" t="n">
+        <s:v>357.29</s:v>
+      </s:c>
+      <s:c r="M12" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N12" s="1" t="n">
+        <s:v>21525.74</s:v>
+      </s:c>
+      <s:c r="O12" s="1" t="n">
+        <s:v>658.86</s:v>
+      </s:c>
+      <s:c r="P12" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="13" s="1" customFormat="1" spans="1:16">
       <s:c r="A13" s="6" t="n">
@@ -4574,17 +4816,39 @@
       <s:c r="E13" s="1" t="n">
         <s:v>404.32</s:v>
       </s:c>
-      <s:c r="F13" s="1"/>
-      <s:c r="G13" s="1"/>
-      <s:c r="H13" s="1"/>
-      <s:c r="I13" s="1"/>
-      <s:c r="J13" s="1"/>
-      <s:c r="K13" s="1"/>
-      <s:c r="L13" s="1"/>
-      <s:c r="M13" s="1"/>
-      <s:c r="N13" s="1"/>
-      <s:c r="O13" s="1"/>
-      <s:c r="P13" s="1"/>
+      <s:c r="F13" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G13" s="1" t="n">
+        <s:v>2201.39</s:v>
+      </s:c>
+      <s:c r="H13" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I13" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J13" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K13" s="1" t="n">
+        <s:v>452</s:v>
+      </s:c>
+      <s:c r="L13" s="1" t="n">
+        <s:v>356.83</s:v>
+      </s:c>
+      <s:c r="M13" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N13" s="1" t="n">
+        <s:v>21163.99</s:v>
+      </s:c>
+      <s:c r="O13" s="1" t="n">
+        <s:v>580.61</s:v>
+      </s:c>
+      <s:c r="P13" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="14" s="1" customFormat="1" spans="1:16">
       <s:c r="A14" s="6" t="n">
@@ -4600,17 +4864,39 @@
       <s:c r="E14" s="1" t="n">
         <s:v>405.52</s:v>
       </s:c>
-      <s:c r="F14" s="1"/>
-      <s:c r="G14" s="1"/>
-      <s:c r="H14" s="1"/>
-      <s:c r="I14" s="1"/>
-      <s:c r="J14" s="1"/>
-      <s:c r="K14" s="1"/>
-      <s:c r="L14" s="1"/>
-      <s:c r="M14" s="1"/>
-      <s:c r="N14" s="1"/>
-      <s:c r="O14" s="1"/>
-      <s:c r="P14" s="1"/>
+      <s:c r="F14" s="1" t="n">
+        <s:v>120</s:v>
+      </s:c>
+      <s:c r="G14" s="1" t="n">
+        <s:v>2194.03</s:v>
+      </s:c>
+      <s:c r="H14" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I14" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L14" s="1" t="n">
+        <s:v>355.88</s:v>
+      </s:c>
+      <s:c r="M14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N14" s="1" t="n">
+        <s:v>21240.17</s:v>
+      </s:c>
+      <s:c r="O14" s="1" t="n">
+        <s:v>515.54</s:v>
+      </s:c>
+      <s:c r="P14" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="15" s="1" customFormat="1" spans="1:16">
       <s:c r="A15" s="6" t="n">
@@ -4626,17 +4912,39 @@
       <s:c r="E15" s="1" t="n">
         <s:v>404.76</s:v>
       </s:c>
-      <s:c r="F15" s="1"/>
-      <s:c r="G15" s="1"/>
-      <s:c r="H15" s="1"/>
-      <s:c r="I15" s="1"/>
-      <s:c r="J15" s="1"/>
-      <s:c r="K15" s="1"/>
-      <s:c r="L15" s="1"/>
-      <s:c r="M15" s="1"/>
-      <s:c r="N15" s="1"/>
-      <s:c r="O15" s="1"/>
-      <s:c r="P15" s="1"/>
+      <s:c r="F15" s="1" t="n">
+        <s:v>300</s:v>
+      </s:c>
+      <s:c r="G15" s="1" t="n">
+        <s:v>2160.46</s:v>
+      </s:c>
+      <s:c r="H15" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I15" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L15" s="1" t="n">
+        <s:v>358.07</s:v>
+      </s:c>
+      <s:c r="M15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N15" s="1" t="n">
+        <s:v>21185.3</s:v>
+      </s:c>
+      <s:c r="O15" s="1" t="n">
+        <s:v>453.87</s:v>
+      </s:c>
+      <s:c r="P15" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="16" s="1" customFormat="1" spans="1:16">
       <s:c r="A16" s="6" t="n">
@@ -4652,17 +4960,39 @@
       <s:c r="E16" s="1" t="n">
         <s:v>403.19</s:v>
       </s:c>
-      <s:c r="F16" s="1"/>
-      <s:c r="G16" s="1"/>
-      <s:c r="H16" s="1"/>
-      <s:c r="I16" s="1"/>
-      <s:c r="J16" s="1"/>
-      <s:c r="K16" s="1"/>
-      <s:c r="L16" s="1"/>
-      <s:c r="M16" s="1"/>
-      <s:c r="N16" s="1"/>
-      <s:c r="O16" s="1"/>
-      <s:c r="P16" s="1"/>
+      <s:c r="F16" s="1" t="n">
+        <s:v>660</s:v>
+      </s:c>
+      <s:c r="G16" s="1" t="n">
+        <s:v>2194.76</s:v>
+      </s:c>
+      <s:c r="H16" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I16" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L16" s="1" t="n">
+        <s:v>357.45</s:v>
+      </s:c>
+      <s:c r="M16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N16" s="1" t="n">
+        <s:v>20858.84</s:v>
+      </s:c>
+      <s:c r="O16" s="1" t="n">
+        <s:v>405.36</s:v>
+      </s:c>
+      <s:c r="P16" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="17" s="1" customFormat="1" spans="1:16">
       <s:c r="A17" s="6" t="n">
@@ -4678,17 +5008,39 @@
       <s:c r="E17" s="1" t="n">
         <s:v>402.42</s:v>
       </s:c>
-      <s:c r="F17" s="1"/>
-      <s:c r="G17" s="1"/>
-      <s:c r="H17" s="1"/>
-      <s:c r="I17" s="1"/>
-      <s:c r="J17" s="1"/>
-      <s:c r="K17" s="1"/>
-      <s:c r="L17" s="1"/>
-      <s:c r="M17" s="1"/>
-      <s:c r="N17" s="1"/>
-      <s:c r="O17" s="1"/>
-      <s:c r="P17" s="1"/>
+      <s:c r="F17" s="1" t="n">
+        <s:v>843</s:v>
+      </s:c>
+      <s:c r="G17" s="1" t="n">
+        <s:v>2200.05</s:v>
+      </s:c>
+      <s:c r="H17" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I17" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L17" s="1" t="n">
+        <s:v>357.93</s:v>
+      </s:c>
+      <s:c r="M17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N17" s="1" t="n">
+        <s:v>20736.69</s:v>
+      </s:c>
+      <s:c r="O17" s="1" t="n">
+        <s:v>415.63</s:v>
+      </s:c>
+      <s:c r="P17" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="18" s="1" customFormat="1" spans="1:16">
       <s:c r="A18" s="6" t="n">
@@ -4704,17 +5056,39 @@
       <s:c r="E18" s="1" t="n">
         <s:v>403.35</s:v>
       </s:c>
-      <s:c r="F18" s="1"/>
-      <s:c r="G18" s="1"/>
-      <s:c r="H18" s="1"/>
-      <s:c r="I18" s="1"/>
-      <s:c r="J18" s="1"/>
-      <s:c r="K18" s="1"/>
-      <s:c r="L18" s="1"/>
-      <s:c r="M18" s="1"/>
-      <s:c r="N18" s="1"/>
-      <s:c r="O18" s="1"/>
-      <s:c r="P18" s="1"/>
+      <s:c r="F18" s="1" t="n">
+        <s:v>923</s:v>
+      </s:c>
+      <s:c r="G18" s="1" t="n">
+        <s:v>2229.35</s:v>
+      </s:c>
+      <s:c r="H18" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I18" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L18" s="1" t="n">
+        <s:v>356.51</s:v>
+      </s:c>
+      <s:c r="M18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N18" s="1" t="n">
+        <s:v>20901.08</s:v>
+      </s:c>
+      <s:c r="O18" s="1" t="n">
+        <s:v>397.36</s:v>
+      </s:c>
+      <s:c r="P18" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="19" s="1" customFormat="1" spans="1:16">
       <s:c r="A19" s="6" t="n">
@@ -4730,17 +5104,39 @@
       <s:c r="E19" s="1" t="n">
         <s:v>401.36</s:v>
       </s:c>
-      <s:c r="F19" s="1"/>
-      <s:c r="G19" s="1"/>
-      <s:c r="H19" s="1"/>
-      <s:c r="I19" s="1"/>
-      <s:c r="J19" s="1"/>
-      <s:c r="K19" s="1"/>
-      <s:c r="L19" s="1"/>
-      <s:c r="M19" s="1"/>
-      <s:c r="N19" s="1"/>
-      <s:c r="O19" s="1"/>
-      <s:c r="P19" s="1"/>
+      <s:c r="F19" s="1" t="n">
+        <s:v>1003</s:v>
+      </s:c>
+      <s:c r="G19" s="1" t="n">
+        <s:v>2223.82</s:v>
+      </s:c>
+      <s:c r="H19" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I19" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L19" s="1" t="n">
+        <s:v>356.98</s:v>
+      </s:c>
+      <s:c r="M19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N19" s="1" t="n">
+        <s:v>20632.69</s:v>
+      </s:c>
+      <s:c r="O19" s="1" t="n">
+        <s:v>395.52</s:v>
+      </s:c>
+      <s:c r="P19" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="20" s="1" customFormat="1" spans="1:16">
       <s:c r="A20" s="6" t="n">
@@ -4756,17 +5152,39 @@
       <s:c r="E20" s="1" t="n">
         <s:v>399.85</s:v>
       </s:c>
-      <s:c r="F20" s="1"/>
-      <s:c r="G20" s="1"/>
-      <s:c r="H20" s="1"/>
-      <s:c r="I20" s="1"/>
-      <s:c r="J20" s="1"/>
-      <s:c r="K20" s="1"/>
-      <s:c r="L20" s="1"/>
-      <s:c r="M20" s="1"/>
-      <s:c r="N20" s="1"/>
-      <s:c r="O20" s="1"/>
-      <s:c r="P20" s="1"/>
+      <s:c r="F20" s="1" t="n">
+        <s:v>1123</s:v>
+      </s:c>
+      <s:c r="G20" s="1" t="n">
+        <s:v>2238.51</s:v>
+      </s:c>
+      <s:c r="H20" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I20" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L20" s="1" t="n">
+        <s:v>358.08</s:v>
+      </s:c>
+      <s:c r="M20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N20" s="1" t="n">
+        <s:v>20541.2</s:v>
+      </s:c>
+      <s:c r="O20" s="1" t="n">
+        <s:v>370.57</s:v>
+      </s:c>
+      <s:c r="P20" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="21" s="1" customFormat="1" spans="1:16">
       <s:c r="A21" s="6" t="n">
@@ -4782,17 +5200,39 @@
       <s:c r="E21" s="1" t="n">
         <s:v>398.73</s:v>
       </s:c>
-      <s:c r="F21" s="1"/>
-      <s:c r="G21" s="1"/>
-      <s:c r="H21" s="1"/>
-      <s:c r="I21" s="1"/>
-      <s:c r="J21" s="1"/>
-      <s:c r="K21" s="1"/>
-      <s:c r="L21" s="1"/>
-      <s:c r="M21" s="1"/>
-      <s:c r="N21" s="1"/>
-      <s:c r="O21" s="1"/>
-      <s:c r="P21" s="1"/>
+      <s:c r="F21" s="1" t="n">
+        <s:v>1143</s:v>
+      </s:c>
+      <s:c r="G21" s="1" t="n">
+        <s:v>2217.51</s:v>
+      </s:c>
+      <s:c r="H21" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I21" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L21" s="1" t="n">
+        <s:v>357.14</s:v>
+      </s:c>
+      <s:c r="M21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N21" s="1" t="n">
+        <s:v>20320.14</s:v>
+      </s:c>
+      <s:c r="O21" s="1" t="n">
+        <s:v>377.03</s:v>
+      </s:c>
+      <s:c r="P21" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="22" s="1" customFormat="1" spans="1:16">
       <s:c r="A22" s="6" t="n">
@@ -4808,17 +5248,39 @@
       <s:c r="E22" s="1" t="n">
         <s:v>397.73</s:v>
       </s:c>
-      <s:c r="F22" s="1"/>
-      <s:c r="G22" s="1"/>
-      <s:c r="H22" s="1"/>
-      <s:c r="I22" s="1"/>
-      <s:c r="J22" s="1"/>
-      <s:c r="K22" s="1"/>
-      <s:c r="L22" s="1"/>
-      <s:c r="M22" s="1"/>
-      <s:c r="N22" s="1"/>
-      <s:c r="O22" s="1"/>
-      <s:c r="P22" s="1"/>
+      <s:c r="F22" s="1" t="n">
+        <s:v>1523</s:v>
+      </s:c>
+      <s:c r="G22" s="1" t="n">
+        <s:v>2190.59</s:v>
+      </s:c>
+      <s:c r="H22" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I22" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L22" s="1" t="n">
+        <s:v>357.29</s:v>
+      </s:c>
+      <s:c r="M22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N22" s="1" t="n">
+        <s:v>20109.38</s:v>
+      </s:c>
+      <s:c r="O22" s="1" t="n">
+        <s:v>433.91</s:v>
+      </s:c>
+      <s:c r="P22" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="23" s="1" customFormat="1" spans="1:16">
       <s:c r="A23" s="6" t="n">
@@ -4834,17 +5296,39 @@
       <s:c r="E23" s="1" t="n">
         <s:v>400.48</s:v>
       </s:c>
-      <s:c r="F23" s="1"/>
-      <s:c r="G23" s="1"/>
-      <s:c r="H23" s="1"/>
-      <s:c r="I23" s="1"/>
-      <s:c r="J23" s="1"/>
-      <s:c r="K23" s="1"/>
-      <s:c r="L23" s="1"/>
-      <s:c r="M23" s="1"/>
-      <s:c r="N23" s="1"/>
-      <s:c r="O23" s="1"/>
-      <s:c r="P23" s="1"/>
+      <s:c r="F23" s="1" t="n">
+        <s:v>1523</s:v>
+      </s:c>
+      <s:c r="G23" s="1" t="n">
+        <s:v>2213.96</s:v>
+      </s:c>
+      <s:c r="H23" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I23" s="1" t="n">
+        <s:v>3.75</s:v>
+      </s:c>
+      <s:c r="J23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L23" s="1" t="n">
+        <s:v>356.18</s:v>
+      </s:c>
+      <s:c r="M23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N23" s="1" t="n">
+        <s:v>20597.41</s:v>
+      </s:c>
+      <s:c r="O23" s="1" t="n">
+        <s:v>399.47</s:v>
+      </s:c>
+      <s:c r="P23" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="24" s="1" customFormat="1" spans="1:16">
       <s:c r="A24" s="6" t="n">
@@ -4860,17 +5344,39 @@
       <s:c r="E24" s="1" t="n">
         <s:v>397.7</s:v>
       </s:c>
-      <s:c r="F24" s="1"/>
-      <s:c r="G24" s="1"/>
-      <s:c r="H24" s="1"/>
-      <s:c r="I24" s="1"/>
-      <s:c r="J24" s="1"/>
-      <s:c r="K24" s="1"/>
-      <s:c r="L24" s="1"/>
-      <s:c r="M24" s="1"/>
-      <s:c r="N24" s="1"/>
-      <s:c r="O24" s="1"/>
-      <s:c r="P24" s="1"/>
+      <s:c r="F24" s="1" t="n">
+        <s:v>1748</s:v>
+      </s:c>
+      <s:c r="G24" s="1" t="n">
+        <s:v>2208.67</s:v>
+      </s:c>
+      <s:c r="H24" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I24" s="1" t="n">
+        <s:v>3.84</s:v>
+      </s:c>
+      <s:c r="J24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L24" s="1" t="n">
+        <s:v>357.44</s:v>
+      </s:c>
+      <s:c r="M24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N24" s="1" t="n">
+        <s:v>20665.64</s:v>
+      </s:c>
+      <s:c r="O24" s="1" t="n">
+        <s:v>355.23</s:v>
+      </s:c>
+      <s:c r="P24" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="25" s="1" customFormat="1" spans="1:16">
       <s:c r="A25" s="6" t="n">
@@ -4886,17 +5392,39 @@
       <s:c r="E25" s="1" t="n">
         <s:v>395.14</s:v>
       </s:c>
-      <s:c r="F25" s="1"/>
-      <s:c r="G25" s="1"/>
-      <s:c r="H25" s="1"/>
-      <s:c r="I25" s="1"/>
-      <s:c r="J25" s="1"/>
-      <s:c r="K25" s="1"/>
-      <s:c r="L25" s="1"/>
-      <s:c r="M25" s="1"/>
-      <s:c r="N25" s="1"/>
-      <s:c r="O25" s="1"/>
-      <s:c r="P25" s="1"/>
+      <s:c r="F25" s="1" t="n">
+        <s:v>1978</s:v>
+      </s:c>
+      <s:c r="G25" s="1" t="n">
+        <s:v>2191.21</s:v>
+      </s:c>
+      <s:c r="H25" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I25" s="1" t="n">
+        <s:v>93.3</s:v>
+      </s:c>
+      <s:c r="J25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L25" s="1" t="n">
+        <s:v>356.65</s:v>
+      </s:c>
+      <s:c r="M25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N25" s="1" t="n">
+        <s:v>20438.17</s:v>
+      </s:c>
+      <s:c r="O25" s="1" t="n">
+        <s:v>369.31</s:v>
+      </s:c>
+      <s:c r="P25" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="26" s="1" customFormat="1" spans="1:16">
       <s:c r="A26" s="6" t="n">
@@ -4912,17 +5440,39 @@
       <s:c r="E26" s="1" t="n">
         <s:v>397.27</s:v>
       </s:c>
-      <s:c r="F26" s="1"/>
-      <s:c r="G26" s="1"/>
-      <s:c r="H26" s="1"/>
-      <s:c r="I26" s="1"/>
-      <s:c r="J26" s="1"/>
-      <s:c r="K26" s="1"/>
-      <s:c r="L26" s="1"/>
-      <s:c r="M26" s="1"/>
-      <s:c r="N26" s="1"/>
-      <s:c r="O26" s="1"/>
-      <s:c r="P26" s="1"/>
+      <s:c r="F26" s="1" t="n">
+        <s:v>1908</s:v>
+      </s:c>
+      <s:c r="G26" s="1" t="n">
+        <s:v>2197.31</s:v>
+      </s:c>
+      <s:c r="H26" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I26" s="1" t="n">
+        <s:v>225.67</s:v>
+      </s:c>
+      <s:c r="J26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L26" s="1" t="n">
+        <s:v>358.07</s:v>
+      </s:c>
+      <s:c r="M26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N26" s="1" t="n">
+        <s:v>20317.7</s:v>
+      </s:c>
+      <s:c r="O26" s="1" t="n">
+        <s:v>358.92</s:v>
+      </s:c>
+      <s:c r="P26" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="27" s="1" customFormat="1" spans="1:16">
       <s:c r="A27" s="6" t="n">
@@ -4938,17 +5488,39 @@
       <s:c r="E27" s="1" t="n">
         <s:v>397.73</s:v>
       </s:c>
-      <s:c r="F27" s="1"/>
-      <s:c r="G27" s="1"/>
-      <s:c r="H27" s="1"/>
-      <s:c r="I27" s="1"/>
-      <s:c r="J27" s="1"/>
-      <s:c r="K27" s="1"/>
-      <s:c r="L27" s="1"/>
-      <s:c r="M27" s="1"/>
-      <s:c r="N27" s="1"/>
-      <s:c r="O27" s="1"/>
-      <s:c r="P27" s="1"/>
+      <s:c r="F27" s="1" t="n">
+        <s:v>1818</s:v>
+      </s:c>
+      <s:c r="G27" s="1" t="n">
+        <s:v>2241.06</s:v>
+      </s:c>
+      <s:c r="H27" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I27" s="1" t="n">
+        <s:v>505</s:v>
+      </s:c>
+      <s:c r="J27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L27" s="1" t="n">
+        <s:v>213.03</s:v>
+      </s:c>
+      <s:c r="M27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N27" s="1" t="n">
+        <s:v>20185.28</s:v>
+      </s:c>
+      <s:c r="O27" s="1" t="n">
+        <s:v>284.01</s:v>
+      </s:c>
+      <s:c r="P27" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="28" s="1" customFormat="1" spans="1:16">
       <s:c r="A28" s="6" t="n">
@@ -4964,17 +5536,39 @@
       <s:c r="E28" s="1" t="n">
         <s:v>395.07</s:v>
       </s:c>
-      <s:c r="F28" s="1"/>
-      <s:c r="G28" s="1"/>
-      <s:c r="H28" s="1"/>
-      <s:c r="I28" s="1"/>
-      <s:c r="J28" s="1"/>
-      <s:c r="K28" s="1"/>
-      <s:c r="L28" s="1"/>
-      <s:c r="M28" s="1"/>
-      <s:c r="N28" s="1"/>
-      <s:c r="O28" s="1"/>
-      <s:c r="P28" s="1"/>
+      <s:c r="F28" s="1" t="n">
+        <s:v>1623</s:v>
+      </s:c>
+      <s:c r="G28" s="1" t="n">
+        <s:v>2309.45</s:v>
+      </s:c>
+      <s:c r="H28" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I28" s="1" t="n">
+        <s:v>842.87</s:v>
+      </s:c>
+      <s:c r="J28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N28" s="1" t="n">
+        <s:v>19779.33</s:v>
+      </s:c>
+      <s:c r="O28" s="1" t="n">
+        <s:v>284.21</s:v>
+      </s:c>
+      <s:c r="P28" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="29" s="1" customFormat="1" spans="1:16">
       <s:c r="A29" s="6" t="n">
@@ -4990,17 +5584,39 @@
       <s:c r="E29" s="1" t="n">
         <s:v>383.25</s:v>
       </s:c>
-      <s:c r="F29" s="1"/>
-      <s:c r="G29" s="1"/>
-      <s:c r="H29" s="1"/>
-      <s:c r="I29" s="1"/>
-      <s:c r="J29" s="1"/>
-      <s:c r="K29" s="1"/>
-      <s:c r="L29" s="1"/>
-      <s:c r="M29" s="1"/>
-      <s:c r="N29" s="1"/>
-      <s:c r="O29" s="1"/>
-      <s:c r="P29" s="1"/>
+      <s:c r="F29" s="1" t="n">
+        <s:v>1623</s:v>
+      </s:c>
+      <s:c r="G29" s="1" t="n">
+        <s:v>2372.71</s:v>
+      </s:c>
+      <s:c r="H29" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I29" s="1" t="n">
+        <s:v>1303.19</s:v>
+      </s:c>
+      <s:c r="J29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N29" s="1" t="n">
+        <s:v>18204.14</s:v>
+      </s:c>
+      <s:c r="O29" s="1" t="n">
+        <s:v>286.86</s:v>
+      </s:c>
+      <s:c r="P29" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="30" s="1" customFormat="1" spans="1:16">
       <s:c r="A30" s="6" t="n">
@@ -5016,17 +5632,39 @@
       <s:c r="E30" s="1" t="n">
         <s:v>389.64</s:v>
       </s:c>
-      <s:c r="F30" s="1"/>
-      <s:c r="G30" s="1"/>
-      <s:c r="H30" s="1"/>
-      <s:c r="I30" s="1"/>
-      <s:c r="J30" s="1"/>
-      <s:c r="K30" s="1"/>
-      <s:c r="L30" s="1"/>
-      <s:c r="M30" s="1"/>
-      <s:c r="N30" s="1"/>
-      <s:c r="O30" s="1"/>
-      <s:c r="P30" s="1"/>
+      <s:c r="F30" s="1" t="n">
+        <s:v>1333</s:v>
+      </s:c>
+      <s:c r="G30" s="1" t="n">
+        <s:v>2406.3</s:v>
+      </s:c>
+      <s:c r="H30" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I30" s="1" t="n">
+        <s:v>1845.36</s:v>
+      </s:c>
+      <s:c r="J30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N30" s="1" t="n">
+        <s:v>18611.09</s:v>
+      </s:c>
+      <s:c r="O30" s="1" t="n">
+        <s:v>213.85</s:v>
+      </s:c>
+      <s:c r="P30" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="31" s="1" customFormat="1" spans="1:16">
       <s:c r="A31" s="6" t="n">
@@ -5042,17 +5680,39 @@
       <s:c r="E31" s="1" t="n">
         <s:v>393.23</s:v>
       </s:c>
-      <s:c r="F31" s="1"/>
-      <s:c r="G31" s="1"/>
-      <s:c r="H31" s="1"/>
-      <s:c r="I31" s="1"/>
-      <s:c r="J31" s="1"/>
-      <s:c r="K31" s="1"/>
-      <s:c r="L31" s="1"/>
-      <s:c r="M31" s="1"/>
-      <s:c r="N31" s="1"/>
-      <s:c r="O31" s="1"/>
-      <s:c r="P31" s="1"/>
+      <s:c r="F31" s="1" t="n">
+        <s:v>1243</s:v>
+      </s:c>
+      <s:c r="G31" s="1" t="n">
+        <s:v>2452.29</s:v>
+      </s:c>
+      <s:c r="H31" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I31" s="1" t="n">
+        <s:v>2378.03</s:v>
+      </s:c>
+      <s:c r="J31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N31" s="1" t="n">
+        <s:v>19139.28</s:v>
+      </s:c>
+      <s:c r="O31" s="1" t="n">
+        <s:v>184.9</s:v>
+      </s:c>
+      <s:c r="P31" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="32" s="1" customFormat="1" spans="1:16">
       <s:c r="A32" s="6" t="n">
@@ -5068,17 +5728,39 @@
       <s:c r="E32" s="1" t="n">
         <s:v>390</s:v>
       </s:c>
-      <s:c r="F32" s="1"/>
-      <s:c r="G32" s="1"/>
-      <s:c r="H32" s="1"/>
-      <s:c r="I32" s="1"/>
-      <s:c r="J32" s="1"/>
-      <s:c r="K32" s="1"/>
-      <s:c r="L32" s="1"/>
-      <s:c r="M32" s="1"/>
-      <s:c r="N32" s="1"/>
-      <s:c r="O32" s="1"/>
-      <s:c r="P32" s="1"/>
+      <s:c r="F32" s="1" t="n">
+        <s:v>760</s:v>
+      </s:c>
+      <s:c r="G32" s="1" t="n">
+        <s:v>2509.42</s:v>
+      </s:c>
+      <s:c r="H32" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I32" s="1" t="n">
+        <s:v>2854.05</s:v>
+      </s:c>
+      <s:c r="J32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N32" s="1" t="n">
+        <s:v>18758.45</s:v>
+      </s:c>
+      <s:c r="O32" s="1" t="n">
+        <s:v>193.58</s:v>
+      </s:c>
+      <s:c r="P32" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="33" s="1" customFormat="1" spans="1:16">
       <s:c r="A33" s="6" t="n">
@@ -5094,17 +5776,39 @@
       <s:c r="E33" s="1" t="n">
         <s:v>390</s:v>
       </s:c>
-      <s:c r="F33" s="1"/>
-      <s:c r="G33" s="1"/>
-      <s:c r="H33" s="1"/>
-      <s:c r="I33" s="1"/>
-      <s:c r="J33" s="1"/>
-      <s:c r="K33" s="1"/>
-      <s:c r="L33" s="1"/>
-      <s:c r="M33" s="1"/>
-      <s:c r="N33" s="1"/>
-      <s:c r="O33" s="1"/>
-      <s:c r="P33" s="1"/>
+      <s:c r="F33" s="1" t="n">
+        <s:v>360</s:v>
+      </s:c>
+      <s:c r="G33" s="1" t="n">
+        <s:v>2508.55</s:v>
+      </s:c>
+      <s:c r="H33" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I33" s="1" t="n">
+        <s:v>3452.41</s:v>
+      </s:c>
+      <s:c r="J33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N33" s="1" t="n">
+        <s:v>18297.6</s:v>
+      </s:c>
+      <s:c r="O33" s="1" t="n">
+        <s:v>194.55</s:v>
+      </s:c>
+      <s:c r="P33" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="34" s="1" customFormat="1" spans="1:16">
       <s:c r="A34" s="6" t="n">
@@ -5120,17 +5824,39 @@
       <s:c r="E34" s="1" t="n">
         <s:v>386.97</s:v>
       </s:c>
-      <s:c r="F34" s="1"/>
-      <s:c r="G34" s="1"/>
-      <s:c r="H34" s="1"/>
-      <s:c r="I34" s="1"/>
-      <s:c r="J34" s="1"/>
-      <s:c r="K34" s="1"/>
-      <s:c r="L34" s="1"/>
-      <s:c r="M34" s="1"/>
-      <s:c r="N34" s="1"/>
-      <s:c r="O34" s="1"/>
-      <s:c r="P34" s="1"/>
+      <s:c r="F34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G34" s="1" t="n">
+        <s:v>2551.85</s:v>
+      </s:c>
+      <s:c r="H34" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I34" s="1" t="n">
+        <s:v>4224.02</s:v>
+      </s:c>
+      <s:c r="J34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N34" s="1" t="n">
+        <s:v>17516.52</s:v>
+      </s:c>
+      <s:c r="O34" s="1" t="n">
+        <s:v>189.32</s:v>
+      </s:c>
+      <s:c r="P34" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="35" s="1" customFormat="1" spans="1:16">
       <s:c r="A35" s="6" t="n">
@@ -5146,17 +5872,39 @@
       <s:c r="E35" s="1" t="n">
         <s:v>380.57</s:v>
       </s:c>
-      <s:c r="F35" s="1"/>
-      <s:c r="G35" s="1"/>
-      <s:c r="H35" s="1"/>
-      <s:c r="I35" s="1"/>
-      <s:c r="J35" s="1"/>
-      <s:c r="K35" s="1"/>
-      <s:c r="L35" s="1"/>
-      <s:c r="M35" s="1"/>
-      <s:c r="N35" s="1"/>
-      <s:c r="O35" s="1"/>
-      <s:c r="P35" s="1"/>
+      <s:c r="F35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G35" s="1" t="n">
+        <s:v>2579.98</s:v>
+      </s:c>
+      <s:c r="H35" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I35" s="1" t="n">
+        <s:v>4927.25</s:v>
+      </s:c>
+      <s:c r="J35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N35" s="1" t="n">
+        <s:v>16542.5</s:v>
+      </s:c>
+      <s:c r="O35" s="1" t="n">
+        <s:v>195.47</s:v>
+      </s:c>
+      <s:c r="P35" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="36" s="1" customFormat="1" spans="1:16">
       <s:c r="A36" s="6" t="n">
@@ -5172,17 +5920,39 @@
       <s:c r="E36" s="1" t="n">
         <s:v>378.77</s:v>
       </s:c>
-      <s:c r="F36" s="1"/>
-      <s:c r="G36" s="1"/>
-      <s:c r="H36" s="1"/>
-      <s:c r="I36" s="1"/>
-      <s:c r="J36" s="1"/>
-      <s:c r="K36" s="1"/>
-      <s:c r="L36" s="1"/>
-      <s:c r="M36" s="1"/>
-      <s:c r="N36" s="1"/>
-      <s:c r="O36" s="1"/>
-      <s:c r="P36" s="1"/>
+      <s:c r="F36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G36" s="1" t="n">
+        <s:v>2594.43</s:v>
+      </s:c>
+      <s:c r="H36" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I36" s="1" t="n">
+        <s:v>5266.41</s:v>
+      </s:c>
+      <s:c r="J36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N36" s="1" t="n">
+        <s:v>16112.38</s:v>
+      </s:c>
+      <s:c r="O36" s="1" t="n">
+        <s:v>181.5</s:v>
+      </s:c>
+      <s:c r="P36" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="37" s="1" customFormat="1" spans="1:16">
       <s:c r="A37" s="6" t="n">
@@ -5198,17 +5968,39 @@
       <s:c r="E37" s="1" t="n">
         <s:v>376.01</s:v>
       </s:c>
-      <s:c r="F37" s="1"/>
-      <s:c r="G37" s="1"/>
-      <s:c r="H37" s="1"/>
-      <s:c r="I37" s="1"/>
-      <s:c r="J37" s="1"/>
-      <s:c r="K37" s="1"/>
-      <s:c r="L37" s="1"/>
-      <s:c r="M37" s="1"/>
-      <s:c r="N37" s="1"/>
-      <s:c r="O37" s="1"/>
-      <s:c r="P37" s="1"/>
+      <s:c r="F37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G37" s="1" t="n">
+        <s:v>2632.07</s:v>
+      </s:c>
+      <s:c r="H37" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I37" s="1" t="n">
+        <s:v>5778.18</s:v>
+      </s:c>
+      <s:c r="J37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K37" s="1" t="n">
+        <s:v>-26.3</s:v>
+      </s:c>
+      <s:c r="L37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N37" s="1" t="n">
+        <s:v>15398.35</s:v>
+      </s:c>
+      <s:c r="O37" s="1" t="n">
+        <s:v>140.21</s:v>
+      </s:c>
+      <s:c r="P37" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="38" s="1" customFormat="1" spans="1:16">
       <s:c r="A38" s="6" t="n">
@@ -5224,17 +6016,39 @@
       <s:c r="E38" s="1" t="n">
         <s:v>373.11</s:v>
       </s:c>
-      <s:c r="F38" s="1"/>
-      <s:c r="G38" s="1"/>
-      <s:c r="H38" s="1"/>
-      <s:c r="I38" s="1"/>
-      <s:c r="J38" s="1"/>
-      <s:c r="K38" s="1"/>
-      <s:c r="L38" s="1"/>
-      <s:c r="M38" s="1"/>
-      <s:c r="N38" s="1"/>
-      <s:c r="O38" s="1"/>
-      <s:c r="P38" s="1"/>
+      <s:c r="F38" s="1" t="n">
+        <s:v>-420</s:v>
+      </s:c>
+      <s:c r="G38" s="1" t="n">
+        <s:v>2674.34</s:v>
+      </s:c>
+      <s:c r="H38" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I38" s="1" t="n">
+        <s:v>6431.09</s:v>
+      </s:c>
+      <s:c r="J38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K38" s="1" t="n">
+        <s:v>-586.1</s:v>
+      </s:c>
+      <s:c r="L38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N38" s="1" t="n">
+        <s:v>14986.51</s:v>
+      </s:c>
+      <s:c r="O38" s="1" t="n">
+        <s:v>133.57</s:v>
+      </s:c>
+      <s:c r="P38" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="39" s="1" customFormat="1" spans="1:16">
       <s:c r="A39" s="6" t="n">
@@ -5250,17 +6064,39 @@
       <s:c r="E39" s="1" t="n">
         <s:v>379.38</s:v>
       </s:c>
-      <s:c r="F39" s="1"/>
-      <s:c r="G39" s="1"/>
-      <s:c r="H39" s="1"/>
-      <s:c r="I39" s="1"/>
-      <s:c r="J39" s="1"/>
-      <s:c r="K39" s="1"/>
-      <s:c r="L39" s="1"/>
-      <s:c r="M39" s="1"/>
-      <s:c r="N39" s="1"/>
-      <s:c r="O39" s="1"/>
-      <s:c r="P39" s="1"/>
+      <s:c r="F39" s="1" t="n">
+        <s:v>-660</s:v>
+      </s:c>
+      <s:c r="G39" s="1" t="n">
+        <s:v>2712.14</s:v>
+      </s:c>
+      <s:c r="H39" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I39" s="1" t="n">
+        <s:v>6776.88</s:v>
+      </s:c>
+      <s:c r="J39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K39" s="1" t="n">
+        <s:v>-1117.9</s:v>
+      </s:c>
+      <s:c r="L39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N39" s="1" t="n">
+        <s:v>15598.72</s:v>
+      </s:c>
+      <s:c r="O39" s="1" t="n">
+        <s:v>127.77</s:v>
+      </s:c>
+      <s:c r="P39" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="40" s="1" customFormat="1" spans="1:16">
       <s:c r="A40" s="6" t="n">
@@ -5276,17 +6112,39 @@
       <s:c r="E40" s="1" t="n">
         <s:v>379.79</s:v>
       </s:c>
-      <s:c r="F40" s="1"/>
-      <s:c r="G40" s="1"/>
-      <s:c r="H40" s="1"/>
-      <s:c r="I40" s="1"/>
-      <s:c r="J40" s="1"/>
-      <s:c r="K40" s="1"/>
-      <s:c r="L40" s="1"/>
-      <s:c r="M40" s="1"/>
-      <s:c r="N40" s="1"/>
-      <s:c r="O40" s="1"/>
-      <s:c r="P40" s="1"/>
+      <s:c r="F40" s="1" t="n">
+        <s:v>-853</s:v>
+      </s:c>
+      <s:c r="G40" s="1" t="n">
+        <s:v>2663.03</s:v>
+      </s:c>
+      <s:c r="H40" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I40" s="1" t="n">
+        <s:v>7056.47</s:v>
+      </s:c>
+      <s:c r="J40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K40" s="1" t="n">
+        <s:v>-1119.9</s:v>
+      </s:c>
+      <s:c r="L40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N40" s="1" t="n">
+        <s:v>15794.2</s:v>
+      </s:c>
+      <s:c r="O40" s="1" t="n">
+        <s:v>115.81</s:v>
+      </s:c>
+      <s:c r="P40" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="41" s="1" customFormat="1" spans="1:16">
       <s:c r="A41" s="6" t="n">
@@ -5302,17 +6160,39 @@
       <s:c r="E41" s="1" t="n">
         <s:v>373.48</s:v>
       </s:c>
-      <s:c r="F41" s="1"/>
-      <s:c r="G41" s="1"/>
-      <s:c r="H41" s="1"/>
-      <s:c r="I41" s="1"/>
-      <s:c r="J41" s="1"/>
-      <s:c r="K41" s="1"/>
-      <s:c r="L41" s="1"/>
-      <s:c r="M41" s="1"/>
-      <s:c r="N41" s="1"/>
-      <s:c r="O41" s="1"/>
-      <s:c r="P41" s="1"/>
+      <s:c r="F41" s="1" t="n">
+        <s:v>-963</s:v>
+      </s:c>
+      <s:c r="G41" s="1" t="n">
+        <s:v>2705.97</s:v>
+      </s:c>
+      <s:c r="H41" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I41" s="1" t="n">
+        <s:v>7233.08</s:v>
+      </s:c>
+      <s:c r="J41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K41" s="1" t="n">
+        <s:v>-1116.5</s:v>
+      </s:c>
+      <s:c r="L41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N41" s="1" t="n">
+        <s:v>15142.62</s:v>
+      </s:c>
+      <s:c r="O41" s="1" t="n">
+        <s:v>115.04</s:v>
+      </s:c>
+      <s:c r="P41" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="42" s="1" customFormat="1" spans="1:16">
       <s:c r="A42" s="6" t="n">
@@ -5328,17 +6208,39 @@
       <s:c r="E42" s="1" t="n">
         <s:v>371.8</s:v>
       </s:c>
-      <s:c r="F42" s="1"/>
-      <s:c r="G42" s="1"/>
-      <s:c r="H42" s="1"/>
-      <s:c r="I42" s="1"/>
-      <s:c r="J42" s="1"/>
-      <s:c r="K42" s="1"/>
-      <s:c r="L42" s="1"/>
-      <s:c r="M42" s="1"/>
-      <s:c r="N42" s="1"/>
-      <s:c r="O42" s="1"/>
-      <s:c r="P42" s="1"/>
+      <s:c r="F42" s="1" t="n">
+        <s:v>-1053</s:v>
+      </s:c>
+      <s:c r="G42" s="1" t="n">
+        <s:v>2761.43</s:v>
+      </s:c>
+      <s:c r="H42" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I42" s="1" t="n">
+        <s:v>7652.05</s:v>
+      </s:c>
+      <s:c r="J42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K42" s="1" t="n">
+        <s:v>-1111.1</s:v>
+      </s:c>
+      <s:c r="L42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N42" s="1" t="n">
+        <s:v>14727.08</s:v>
+      </s:c>
+      <s:c r="O42" s="1" t="n">
+        <s:v>116.95</s:v>
+      </s:c>
+      <s:c r="P42" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="43" s="1" customFormat="1" spans="1:16">
       <s:c r="A43" s="6" t="n">
@@ -5354,17 +6256,39 @@
       <s:c r="E43" s="1" t="n">
         <s:v>371.52</s:v>
       </s:c>
-      <s:c r="F43" s="1"/>
-      <s:c r="G43" s="1"/>
-      <s:c r="H43" s="1"/>
-      <s:c r="I43" s="1"/>
-      <s:c r="J43" s="1"/>
-      <s:c r="K43" s="1"/>
-      <s:c r="L43" s="1"/>
-      <s:c r="M43" s="1"/>
-      <s:c r="N43" s="1"/>
-      <s:c r="O43" s="1"/>
-      <s:c r="P43" s="1"/>
+      <s:c r="F43" s="1" t="n">
+        <s:v>-1053</s:v>
+      </s:c>
+      <s:c r="G43" s="1" t="n">
+        <s:v>2772.85</s:v>
+      </s:c>
+      <s:c r="H43" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I43" s="1" t="n">
+        <s:v>7888.24</s:v>
+      </s:c>
+      <s:c r="J43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K43" s="1" t="n">
+        <s:v>-1114.7</s:v>
+      </s:c>
+      <s:c r="L43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N43" s="1" t="n">
+        <s:v>14798.73</s:v>
+      </s:c>
+      <s:c r="O43" s="1" t="n">
+        <s:v>106.38</s:v>
+      </s:c>
+      <s:c r="P43" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="44" s="1" customFormat="1" spans="1:16">
       <s:c r="A44" s="6" t="n">
@@ -5380,17 +6304,39 @@
       <s:c r="E44" s="1" t="n">
         <s:v>368</s:v>
       </s:c>
-      <s:c r="F44" s="1"/>
-      <s:c r="G44" s="1"/>
-      <s:c r="H44" s="1"/>
-      <s:c r="I44" s="1"/>
-      <s:c r="J44" s="1"/>
-      <s:c r="K44" s="1"/>
-      <s:c r="L44" s="1"/>
-      <s:c r="M44" s="1"/>
-      <s:c r="N44" s="1"/>
-      <s:c r="O44" s="1"/>
-      <s:c r="P44" s="1"/>
+      <s:c r="F44" s="1" t="n">
+        <s:v>-1023</s:v>
+      </s:c>
+      <s:c r="G44" s="1" t="n">
+        <s:v>2821.13</s:v>
+      </s:c>
+      <s:c r="H44" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I44" s="1" t="n">
+        <s:v>8299.02</s:v>
+      </s:c>
+      <s:c r="J44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K44" s="1" t="n">
+        <s:v>-1112.1</s:v>
+      </s:c>
+      <s:c r="L44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N44" s="1" t="n">
+        <s:v>14511.58</s:v>
+      </s:c>
+      <s:c r="O44" s="1" t="n">
+        <s:v>105.98</s:v>
+      </s:c>
+      <s:c r="P44" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="45" s="1" customFormat="1" spans="1:16">
       <s:c r="A45" s="6" t="n">
@@ -5406,17 +6352,39 @@
       <s:c r="E45" s="1" t="n">
         <s:v>367.23</s:v>
       </s:c>
-      <s:c r="F45" s="1"/>
-      <s:c r="G45" s="1"/>
-      <s:c r="H45" s="1"/>
-      <s:c r="I45" s="1"/>
-      <s:c r="J45" s="1"/>
-      <s:c r="K45" s="1"/>
-      <s:c r="L45" s="1"/>
-      <s:c r="M45" s="1"/>
-      <s:c r="N45" s="1"/>
-      <s:c r="O45" s="1"/>
-      <s:c r="P45" s="1"/>
+      <s:c r="F45" s="1" t="n">
+        <s:v>-993</s:v>
+      </s:c>
+      <s:c r="G45" s="1" t="n">
+        <s:v>2873.68</s:v>
+      </s:c>
+      <s:c r="H45" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I45" s="1" t="n">
+        <s:v>8493.69</s:v>
+      </s:c>
+      <s:c r="J45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K45" s="1" t="n">
+        <s:v>-1107.4</s:v>
+      </s:c>
+      <s:c r="L45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N45" s="1" t="n">
+        <s:v>14344.72</s:v>
+      </s:c>
+      <s:c r="O45" s="1" t="n">
+        <s:v>101.53</s:v>
+      </s:c>
+      <s:c r="P45" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="46" s="1" customFormat="1" spans="1:16">
       <s:c r="A46" s="6" t="n">
@@ -5432,17 +6400,39 @@
       <s:c r="E46" s="1" t="n">
         <s:v>369.83</s:v>
       </s:c>
-      <s:c r="F46" s="1"/>
-      <s:c r="G46" s="1"/>
-      <s:c r="H46" s="1"/>
-      <s:c r="I46" s="1"/>
-      <s:c r="J46" s="1"/>
-      <s:c r="K46" s="1"/>
-      <s:c r="L46" s="1"/>
-      <s:c r="M46" s="1"/>
-      <s:c r="N46" s="1"/>
-      <s:c r="O46" s="1"/>
-      <s:c r="P46" s="1"/>
+      <s:c r="F46" s="1" t="n">
+        <s:v>-943</s:v>
+      </s:c>
+      <s:c r="G46" s="1" t="n">
+        <s:v>2884.99</s:v>
+      </s:c>
+      <s:c r="H46" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I46" s="1" t="n">
+        <s:v>9002.35</s:v>
+      </s:c>
+      <s:c r="J46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K46" s="1" t="n">
+        <s:v>-1103</s:v>
+      </s:c>
+      <s:c r="L46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N46" s="1" t="n">
+        <s:v>15527.17</s:v>
+      </s:c>
+      <s:c r="O46" s="1" t="n">
+        <s:v>100.91</s:v>
+      </s:c>
+      <s:c r="P46" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="47" s="1" customFormat="1" spans="1:16">
       <s:c r="A47" s="6" t="n">
@@ -5458,17 +6448,39 @@
       <s:c r="E47" s="1" t="n">
         <s:v>373.55</s:v>
       </s:c>
-      <s:c r="F47" s="1"/>
-      <s:c r="G47" s="1"/>
-      <s:c r="H47" s="1"/>
-      <s:c r="I47" s="1"/>
-      <s:c r="J47" s="1"/>
-      <s:c r="K47" s="1"/>
-      <s:c r="L47" s="1"/>
-      <s:c r="M47" s="1"/>
-      <s:c r="N47" s="1"/>
-      <s:c r="O47" s="1"/>
-      <s:c r="P47" s="1"/>
+      <s:c r="F47" s="1" t="n">
+        <s:v>-863</s:v>
+      </s:c>
+      <s:c r="G47" s="1" t="n">
+        <s:v>2832.31</s:v>
+      </s:c>
+      <s:c r="H47" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I47" s="1" t="n">
+        <s:v>9276.9</s:v>
+      </s:c>
+      <s:c r="J47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K47" s="1" t="n">
+        <s:v>-1102.6</s:v>
+      </s:c>
+      <s:c r="L47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N47" s="1" t="n">
+        <s:v>16153.27</s:v>
+      </s:c>
+      <s:c r="O47" s="1" t="n">
+        <s:v>100.43</s:v>
+      </s:c>
+      <s:c r="P47" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="48" s="1" customFormat="1" spans="1:16">
       <s:c r="A48" s="6" t="n">
@@ -5484,17 +6496,39 @@
       <s:c r="E48" s="1" t="n">
         <s:v>372.95</s:v>
       </s:c>
-      <s:c r="F48" s="1"/>
-      <s:c r="G48" s="1"/>
-      <s:c r="H48" s="1"/>
-      <s:c r="I48" s="1"/>
-      <s:c r="J48" s="1"/>
-      <s:c r="K48" s="1"/>
-      <s:c r="L48" s="1"/>
-      <s:c r="M48" s="1"/>
-      <s:c r="N48" s="1"/>
-      <s:c r="O48" s="1"/>
-      <s:c r="P48" s="1"/>
+      <s:c r="F48" s="1" t="n">
+        <s:v>-580</s:v>
+      </s:c>
+      <s:c r="G48" s="1" t="n">
+        <s:v>2810.28</s:v>
+      </s:c>
+      <s:c r="H48" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I48" s="1" t="n">
+        <s:v>9169.89</s:v>
+      </s:c>
+      <s:c r="J48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K48" s="1" t="n">
+        <s:v>-1107.1</s:v>
+      </s:c>
+      <s:c r="L48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N48" s="1" t="n">
+        <s:v>16306.8</s:v>
+      </s:c>
+      <s:c r="O48" s="1" t="n">
+        <s:v>106.23</s:v>
+      </s:c>
+      <s:c r="P48" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="49" s="1" customFormat="1" spans="1:16">
       <s:c r="A49" s="6" t="n">
@@ -5510,17 +6544,39 @@
       <s:c r="E49" s="1" t="n">
         <s:v>361.02</s:v>
       </s:c>
-      <s:c r="F49" s="1"/>
-      <s:c r="G49" s="1"/>
-      <s:c r="H49" s="1"/>
-      <s:c r="I49" s="1"/>
-      <s:c r="J49" s="1"/>
-      <s:c r="K49" s="1"/>
-      <s:c r="L49" s="1"/>
-      <s:c r="M49" s="1"/>
-      <s:c r="N49" s="1"/>
-      <s:c r="O49" s="1"/>
-      <s:c r="P49" s="1"/>
+      <s:c r="F49" s="1" t="n">
+        <s:v>-220</s:v>
+      </s:c>
+      <s:c r="G49" s="1" t="n">
+        <s:v>2776.06</s:v>
+      </s:c>
+      <s:c r="H49" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I49" s="1" t="n">
+        <s:v>9215.37</s:v>
+      </s:c>
+      <s:c r="J49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K49" s="1" t="n">
+        <s:v>-1105.8</s:v>
+      </s:c>
+      <s:c r="L49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N49" s="1" t="n">
+        <s:v>16074.54</s:v>
+      </s:c>
+      <s:c r="O49" s="1" t="n">
+        <s:v>115.94</s:v>
+      </s:c>
+      <s:c r="P49" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="50" s="1" customFormat="1" spans="1:16">
       <s:c r="A50" s="6" t="n">
@@ -5536,17 +6592,39 @@
       <s:c r="E50" s="1" t="n">
         <s:v>369.64</s:v>
       </s:c>
-      <s:c r="F50" s="1"/>
-      <s:c r="G50" s="1"/>
-      <s:c r="H50" s="1"/>
-      <s:c r="I50" s="1"/>
-      <s:c r="J50" s="1"/>
-      <s:c r="K50" s="1"/>
-      <s:c r="L50" s="1"/>
-      <s:c r="M50" s="1"/>
-      <s:c r="N50" s="1"/>
-      <s:c r="O50" s="1"/>
-      <s:c r="P50" s="1"/>
+      <s:c r="F50" s="1" t="n">
+        <s:v>-100</s:v>
+      </s:c>
+      <s:c r="G50" s="1" t="n">
+        <s:v>2823.62</s:v>
+      </s:c>
+      <s:c r="H50" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I50" s="1" t="n">
+        <s:v>9069.4</s:v>
+      </s:c>
+      <s:c r="J50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K50" s="1" t="n">
+        <s:v>-1097.8</s:v>
+      </s:c>
+      <s:c r="L50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N50" s="1" t="n">
+        <s:v>16359.49</s:v>
+      </s:c>
+      <s:c r="O50" s="1" t="n">
+        <s:v>120.09</s:v>
+      </s:c>
+      <s:c r="P50" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="51" s="1" customFormat="1" spans="1:16">
       <s:c r="A51" s="6" t="n">
@@ -5562,17 +6640,39 @@
       <s:c r="E51" s="1" t="n">
         <s:v>377.29</s:v>
       </s:c>
-      <s:c r="F51" s="1"/>
-      <s:c r="G51" s="1"/>
-      <s:c r="H51" s="1"/>
-      <s:c r="I51" s="1"/>
-      <s:c r="J51" s="1"/>
-      <s:c r="K51" s="1"/>
-      <s:c r="L51" s="1"/>
-      <s:c r="M51" s="1"/>
-      <s:c r="N51" s="1"/>
-      <s:c r="O51" s="1"/>
-      <s:c r="P51" s="1"/>
+      <s:c r="F51" s="1" t="n">
+        <s:v>-100</s:v>
+      </s:c>
+      <s:c r="G51" s="1" t="n">
+        <s:v>2780.27</s:v>
+      </s:c>
+      <s:c r="H51" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I51" s="1" t="n">
+        <s:v>8799.26</s:v>
+      </s:c>
+      <s:c r="J51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K51" s="1" t="n">
+        <s:v>-1093.7</s:v>
+      </s:c>
+      <s:c r="L51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N51" s="1" t="n">
+        <s:v>16838.24</s:v>
+      </s:c>
+      <s:c r="O51" s="1" t="n">
+        <s:v>123.74</s:v>
+      </s:c>
+      <s:c r="P51" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="52" s="1" customFormat="1" spans="1:16">
       <s:c r="A52" s="6" t="n">
@@ -5588,17 +6688,39 @@
       <s:c r="E52" s="1" t="n">
         <s:v>375.45</s:v>
       </s:c>
-      <s:c r="F52" s="1"/>
-      <s:c r="G52" s="1"/>
-      <s:c r="H52" s="1"/>
-      <s:c r="I52" s="1"/>
-      <s:c r="J52" s="1"/>
-      <s:c r="K52" s="1"/>
-      <s:c r="L52" s="1"/>
-      <s:c r="M52" s="1"/>
-      <s:c r="N52" s="1"/>
-      <s:c r="O52" s="1"/>
-      <s:c r="P52" s="1"/>
+      <s:c r="F52" s="1" t="n">
+        <s:v>-90</s:v>
+      </s:c>
+      <s:c r="G52" s="1" t="n">
+        <s:v>2761.91</s:v>
+      </s:c>
+      <s:c r="H52" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I52" s="1" t="n">
+        <s:v>8551.98</s:v>
+      </s:c>
+      <s:c r="J52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K52" s="1" t="n">
+        <s:v>-796.8</s:v>
+      </s:c>
+      <s:c r="L52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N52" s="1" t="n">
+        <s:v>17245.59</s:v>
+      </s:c>
+      <s:c r="O52" s="1" t="n">
+        <s:v>128.83</s:v>
+      </s:c>
+      <s:c r="P52" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="53" s="1" customFormat="1" spans="1:16">
       <s:c r="A53" s="6" t="n">
@@ -5614,17 +6736,39 @@
       <s:c r="E53" s="1" t="n">
         <s:v>365</s:v>
       </s:c>
-      <s:c r="F53" s="1"/>
-      <s:c r="G53" s="1"/>
-      <s:c r="H53" s="1"/>
-      <s:c r="I53" s="1"/>
-      <s:c r="J53" s="1"/>
-      <s:c r="K53" s="1"/>
-      <s:c r="L53" s="1"/>
-      <s:c r="M53" s="1"/>
-      <s:c r="N53" s="1"/>
-      <s:c r="O53" s="1"/>
-      <s:c r="P53" s="1"/>
+      <s:c r="F53" s="1" t="n">
+        <s:v>-60</s:v>
+      </s:c>
+      <s:c r="G53" s="1" t="n">
+        <s:v>2736.93</s:v>
+      </s:c>
+      <s:c r="H53" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I53" s="1" t="n">
+        <s:v>8378.03</s:v>
+      </s:c>
+      <s:c r="J53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K53" s="1" t="n">
+        <s:v>-830.5</s:v>
+      </s:c>
+      <s:c r="L53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N53" s="1" t="n">
+        <s:v>17301.83</s:v>
+      </s:c>
+      <s:c r="O53" s="1" t="n">
+        <s:v>126.6</s:v>
+      </s:c>
+      <s:c r="P53" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="54" s="1" customFormat="1" spans="1:16">
       <s:c r="A54" s="6" t="n">
@@ -5640,17 +6784,39 @@
       <s:c r="E54" s="1" t="n">
         <s:v>388.32</s:v>
       </s:c>
-      <s:c r="F54" s="1"/>
-      <s:c r="G54" s="1"/>
-      <s:c r="H54" s="1"/>
-      <s:c r="I54" s="1"/>
-      <s:c r="J54" s="1"/>
-      <s:c r="K54" s="1"/>
-      <s:c r="L54" s="1"/>
-      <s:c r="M54" s="1"/>
-      <s:c r="N54" s="1"/>
-      <s:c r="O54" s="1"/>
-      <s:c r="P54" s="1"/>
+      <s:c r="F54" s="1" t="n">
+        <s:v>-30</s:v>
+      </s:c>
+      <s:c r="G54" s="1" t="n">
+        <s:v>2693.47</s:v>
+      </s:c>
+      <s:c r="H54" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I54" s="1" t="n">
+        <s:v>7944.31</s:v>
+      </s:c>
+      <s:c r="J54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K54" s="1" t="n">
+        <s:v>-846.2</s:v>
+      </s:c>
+      <s:c r="L54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N54" s="1" t="n">
+        <s:v>18544.39</s:v>
+      </s:c>
+      <s:c r="O54" s="1" t="n">
+        <s:v>133.83</s:v>
+      </s:c>
+      <s:c r="P54" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="55" s="1" customFormat="1" spans="1:16">
       <s:c r="A55" s="6" t="n">
@@ -5666,17 +6832,39 @@
       <s:c r="E55" s="1" t="n">
         <s:v>365</s:v>
       </s:c>
-      <s:c r="F55" s="1"/>
-      <s:c r="G55" s="1"/>
-      <s:c r="H55" s="1"/>
-      <s:c r="I55" s="1"/>
-      <s:c r="J55" s="1"/>
-      <s:c r="K55" s="1"/>
-      <s:c r="L55" s="1"/>
-      <s:c r="M55" s="1"/>
-      <s:c r="N55" s="1"/>
-      <s:c r="O55" s="1"/>
-      <s:c r="P55" s="1"/>
+      <s:c r="F55" s="1" t="n">
+        <s:v>-30</s:v>
+      </s:c>
+      <s:c r="G55" s="1" t="n">
+        <s:v>2678.78</s:v>
+      </s:c>
+      <s:c r="H55" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I55" s="1" t="n">
+        <s:v>7752.62</s:v>
+      </s:c>
+      <s:c r="J55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K55" s="1" t="n">
+        <s:v>-304.7</s:v>
+      </s:c>
+      <s:c r="L55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N55" s="1" t="n">
+        <s:v>18223.23</s:v>
+      </s:c>
+      <s:c r="O55" s="1" t="n">
+        <s:v>144</s:v>
+      </s:c>
+      <s:c r="P55" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="56" s="1" customFormat="1" spans="1:16">
       <s:c r="A56" s="6" t="n">
@@ -5692,17 +6880,39 @@
       <s:c r="E56" s="1" t="n">
         <s:v>365</s:v>
       </s:c>
-      <s:c r="F56" s="1"/>
-      <s:c r="G56" s="1"/>
-      <s:c r="H56" s="1"/>
-      <s:c r="I56" s="1"/>
-      <s:c r="J56" s="1"/>
-      <s:c r="K56" s="1"/>
-      <s:c r="L56" s="1"/>
-      <s:c r="M56" s="1"/>
-      <s:c r="N56" s="1"/>
-      <s:c r="O56" s="1"/>
-      <s:c r="P56" s="1"/>
+      <s:c r="F56" s="1" t="n">
+        <s:v>-30</s:v>
+      </s:c>
+      <s:c r="G56" s="1" t="n">
+        <s:v>2681.46</s:v>
+      </s:c>
+      <s:c r="H56" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I56" s="1" t="n">
+        <s:v>7414.79</s:v>
+      </s:c>
+      <s:c r="J56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N56" s="1" t="n">
+        <s:v>17826.05</s:v>
+      </s:c>
+      <s:c r="O56" s="1" t="n">
+        <s:v>164.13</s:v>
+      </s:c>
+      <s:c r="P56" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="57" s="1" customFormat="1" spans="1:16">
       <s:c r="A57" s="6" t="n">
@@ -5718,17 +6928,39 @@
       <s:c r="E57" s="1" t="n">
         <s:v>365</s:v>
       </s:c>
-      <s:c r="F57" s="1"/>
-      <s:c r="G57" s="1"/>
-      <s:c r="H57" s="1"/>
-      <s:c r="I57" s="1"/>
-      <s:c r="J57" s="1"/>
-      <s:c r="K57" s="1"/>
-      <s:c r="L57" s="1"/>
-      <s:c r="M57" s="1"/>
-      <s:c r="N57" s="1"/>
-      <s:c r="O57" s="1"/>
-      <s:c r="P57" s="1"/>
+      <s:c r="F57" s="1" t="n">
+        <s:v>-30</s:v>
+      </s:c>
+      <s:c r="G57" s="1" t="n">
+        <s:v>2663.34</s:v>
+      </s:c>
+      <s:c r="H57" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I57" s="1" t="n">
+        <s:v>7272.51</s:v>
+      </s:c>
+      <s:c r="J57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N57" s="1" t="n">
+        <s:v>17292.76</s:v>
+      </s:c>
+      <s:c r="O57" s="1" t="n">
+        <s:v>190.9</s:v>
+      </s:c>
+      <s:c r="P57" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="58" s="1" customFormat="1" spans="1:16">
       <s:c r="A58" s="6" t="n">
@@ -5744,17 +6976,39 @@
       <s:c r="E58" s="1" t="n">
         <s:v>373.42</s:v>
       </s:c>
-      <s:c r="F58" s="1"/>
-      <s:c r="G58" s="1"/>
-      <s:c r="H58" s="1"/>
-      <s:c r="I58" s="1"/>
-      <s:c r="J58" s="1"/>
-      <s:c r="K58" s="1"/>
-      <s:c r="L58" s="1"/>
-      <s:c r="M58" s="1"/>
-      <s:c r="N58" s="1"/>
-      <s:c r="O58" s="1"/>
-      <s:c r="P58" s="1"/>
+      <s:c r="F58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G58" s="1" t="n">
+        <s:v>2652.14</s:v>
+      </s:c>
+      <s:c r="H58" s="1" t="n">
+        <s:v>0.96</s:v>
+      </s:c>
+      <s:c r="I58" s="1" t="n">
+        <s:v>6893.55</s:v>
+      </s:c>
+      <s:c r="J58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N58" s="1" t="n">
+        <s:v>17696.99</s:v>
+      </s:c>
+      <s:c r="O58" s="1" t="n">
+        <s:v>225.77</s:v>
+      </s:c>
+      <s:c r="P58" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="59" s="1" customFormat="1" spans="1:16">
       <s:c r="A59" s="6" t="n">
@@ -5770,17 +7024,39 @@
       <s:c r="E59" s="1" t="n">
         <s:v>379.67</s:v>
       </s:c>
-      <s:c r="F59" s="1"/>
-      <s:c r="G59" s="1"/>
-      <s:c r="H59" s="1"/>
-      <s:c r="I59" s="1"/>
-      <s:c r="J59" s="1"/>
-      <s:c r="K59" s="1"/>
-      <s:c r="L59" s="1"/>
-      <s:c r="M59" s="1"/>
-      <s:c r="N59" s="1"/>
-      <s:c r="O59" s="1"/>
-      <s:c r="P59" s="1"/>
+      <s:c r="F59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G59" s="1" t="n">
+        <s:v>2644.79</s:v>
+      </s:c>
+      <s:c r="H59" s="1" t="n">
+        <s:v>0.96</s:v>
+      </s:c>
+      <s:c r="I59" s="1" t="n">
+        <s:v>6437.53</s:v>
+      </s:c>
+      <s:c r="J59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N59" s="1" t="n">
+        <s:v>18386.83</s:v>
+      </s:c>
+      <s:c r="O59" s="1" t="n">
+        <s:v>263.09</s:v>
+      </s:c>
+      <s:c r="P59" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="60" s="1" customFormat="1" spans="1:16">
       <s:c r="A60" s="6" t="n">
@@ -5796,17 +7072,39 @@
       <s:c r="E60" s="1" t="n">
         <s:v>389.76</s:v>
       </s:c>
-      <s:c r="F60" s="1"/>
-      <s:c r="G60" s="1"/>
-      <s:c r="H60" s="1"/>
-      <s:c r="I60" s="1"/>
-      <s:c r="J60" s="1"/>
-      <s:c r="K60" s="1"/>
-      <s:c r="L60" s="1"/>
-      <s:c r="M60" s="1"/>
-      <s:c r="N60" s="1"/>
-      <s:c r="O60" s="1"/>
-      <s:c r="P60" s="1"/>
+      <s:c r="F60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G60" s="1" t="n">
+        <s:v>2567.91</s:v>
+      </s:c>
+      <s:c r="H60" s="1" t="n">
+        <s:v>0.96</s:v>
+      </s:c>
+      <s:c r="I60" s="1" t="n">
+        <s:v>6104.83</s:v>
+      </s:c>
+      <s:c r="J60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N60" s="1" t="n">
+        <s:v>19675.49</s:v>
+      </s:c>
+      <s:c r="O60" s="1" t="n">
+        <s:v>288.71</s:v>
+      </s:c>
+      <s:c r="P60" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="61" s="1" customFormat="1" spans="1:16">
       <s:c r="A61" s="6" t="n">
@@ -5822,17 +7120,39 @@
       <s:c r="E61" s="1" t="n">
         <s:v>390.07</s:v>
       </s:c>
-      <s:c r="F61" s="1"/>
-      <s:c r="G61" s="1"/>
-      <s:c r="H61" s="1"/>
-      <s:c r="I61" s="1"/>
-      <s:c r="J61" s="1"/>
-      <s:c r="K61" s="1"/>
-      <s:c r="L61" s="1"/>
-      <s:c r="M61" s="1"/>
-      <s:c r="N61" s="1"/>
-      <s:c r="O61" s="1"/>
-      <s:c r="P61" s="1"/>
+      <s:c r="F61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G61" s="1" t="n">
+        <s:v>2509.28</s:v>
+      </s:c>
+      <s:c r="H61" s="1" t="n">
+        <s:v>0.96</s:v>
+      </s:c>
+      <s:c r="I61" s="1" t="n">
+        <s:v>5688.67</s:v>
+      </s:c>
+      <s:c r="J61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N61" s="1" t="n">
+        <s:v>20273.5</s:v>
+      </s:c>
+      <s:c r="O61" s="1" t="n">
+        <s:v>354.79</s:v>
+      </s:c>
+      <s:c r="P61" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="62" s="1" customFormat="1" spans="1:16">
       <s:c r="A62" s="6" t="n">
@@ -5848,17 +7168,39 @@
       <s:c r="E62" s="1" t="n">
         <s:v>398.63</s:v>
       </s:c>
-      <s:c r="F62" s="1"/>
-      <s:c r="G62" s="1"/>
-      <s:c r="H62" s="1"/>
-      <s:c r="I62" s="1"/>
-      <s:c r="J62" s="1"/>
-      <s:c r="K62" s="1"/>
-      <s:c r="L62" s="1"/>
-      <s:c r="M62" s="1"/>
-      <s:c r="N62" s="1"/>
-      <s:c r="O62" s="1"/>
-      <s:c r="P62" s="1"/>
+      <s:c r="F62" s="1" t="n">
+        <s:v>300</s:v>
+      </s:c>
+      <s:c r="G62" s="1" t="n">
+        <s:v>2441.42</s:v>
+      </s:c>
+      <s:c r="H62" s="1" t="n">
+        <s:v>0.86</s:v>
+      </s:c>
+      <s:c r="I62" s="1" t="n">
+        <s:v>5055.99</s:v>
+      </s:c>
+      <s:c r="J62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N62" s="1" t="n">
+        <s:v>21034.89</s:v>
+      </s:c>
+      <s:c r="O62" s="1" t="n">
+        <s:v>385.65</s:v>
+      </s:c>
+      <s:c r="P62" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="63" s="1" customFormat="1" spans="1:16">
       <s:c r="A63" s="6" t="n">
@@ -5874,17 +7216,39 @@
       <s:c r="E63" s="1" t="n">
         <s:v>397.73</s:v>
       </s:c>
-      <s:c r="F63" s="1"/>
-      <s:c r="G63" s="1"/>
-      <s:c r="H63" s="1"/>
-      <s:c r="I63" s="1"/>
-      <s:c r="J63" s="1"/>
-      <s:c r="K63" s="1"/>
-      <s:c r="L63" s="1"/>
-      <s:c r="M63" s="1"/>
-      <s:c r="N63" s="1"/>
-      <s:c r="O63" s="1"/>
-      <s:c r="P63" s="1"/>
+      <s:c r="F63" s="1" t="n">
+        <s:v>630</s:v>
+      </s:c>
+      <s:c r="G63" s="1" t="n">
+        <s:v>2399.61</s:v>
+      </s:c>
+      <s:c r="H63" s="1" t="n">
+        <s:v>0.86</s:v>
+      </s:c>
+      <s:c r="I63" s="1" t="n">
+        <s:v>4576.95</s:v>
+      </s:c>
+      <s:c r="J63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L63" s="1" t="n">
+        <s:v>194.67</s:v>
+      </s:c>
+      <s:c r="M63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N63" s="1" t="n">
+        <s:v>21206.31</s:v>
+      </s:c>
+      <s:c r="O63" s="1" t="n">
+        <s:v>399.8</s:v>
+      </s:c>
+      <s:c r="P63" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="64" s="1" customFormat="1" spans="1:16">
       <s:c r="A64" s="6" t="n">
@@ -5900,17 +7264,39 @@
       <s:c r="E64" s="1" t="n">
         <s:v>398.73</s:v>
       </s:c>
-      <s:c r="F64" s="1"/>
-      <s:c r="G64" s="1"/>
-      <s:c r="H64" s="1"/>
-      <s:c r="I64" s="1"/>
-      <s:c r="J64" s="1"/>
-      <s:c r="K64" s="1"/>
-      <s:c r="L64" s="1"/>
-      <s:c r="M64" s="1"/>
-      <s:c r="N64" s="1"/>
-      <s:c r="O64" s="1"/>
-      <s:c r="P64" s="1"/>
+      <s:c r="F64" s="1" t="n">
+        <s:v>740</s:v>
+      </s:c>
+      <s:c r="G64" s="1" t="n">
+        <s:v>2377.77</s:v>
+      </s:c>
+      <s:c r="H64" s="1" t="n">
+        <s:v>0.86</s:v>
+      </s:c>
+      <s:c r="I64" s="1" t="n">
+        <s:v>4101.05</s:v>
+      </s:c>
+      <s:c r="J64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K64" s="1" t="n">
+        <s:v>850.5</s:v>
+      </s:c>
+      <s:c r="L64" s="1" t="n">
+        <s:v>275.62</s:v>
+      </s:c>
+      <s:c r="M64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N64" s="1" t="n">
+        <s:v>21363.57</s:v>
+      </s:c>
+      <s:c r="O64" s="1" t="n">
+        <s:v>457.52</s:v>
+      </s:c>
+      <s:c r="P64" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="65" s="1" customFormat="1" spans="1:16">
       <s:c r="A65" s="6" t="n">
@@ -5926,17 +7312,39 @@
       <s:c r="E65" s="1" t="n">
         <s:v>406.76</s:v>
       </s:c>
-      <s:c r="F65" s="1"/>
-      <s:c r="G65" s="1"/>
-      <s:c r="H65" s="1"/>
-      <s:c r="I65" s="1"/>
-      <s:c r="J65" s="1"/>
-      <s:c r="K65" s="1"/>
-      <s:c r="L65" s="1"/>
-      <s:c r="M65" s="1"/>
-      <s:c r="N65" s="1"/>
-      <s:c r="O65" s="1"/>
-      <s:c r="P65" s="1"/>
+      <s:c r="F65" s="1" t="n">
+        <s:v>750</s:v>
+      </s:c>
+      <s:c r="G65" s="1" t="n">
+        <s:v>2338.6</s:v>
+      </s:c>
+      <s:c r="H65" s="1" t="n">
+        <s:v>0.86</s:v>
+      </s:c>
+      <s:c r="I65" s="1" t="n">
+        <s:v>3583.64</s:v>
+      </s:c>
+      <s:c r="J65" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K65" s="1" t="n">
+        <s:v>1098.1</s:v>
+      </s:c>
+      <s:c r="L65" s="1" t="n">
+        <s:v>75.35</s:v>
+      </s:c>
+      <s:c r="M65" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N65" s="1" t="n">
+        <s:v>21952.23</s:v>
+      </s:c>
+      <s:c r="O65" s="1" t="n">
+        <s:v>473.41</s:v>
+      </s:c>
+      <s:c r="P65" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="66" s="1" customFormat="1" spans="1:16">
       <s:c r="A66" s="6" t="n">
@@ -5952,17 +7360,39 @@
       <s:c r="E66" s="1" t="n">
         <s:v>403.57</s:v>
       </s:c>
-      <s:c r="F66" s="1"/>
-      <s:c r="G66" s="1"/>
-      <s:c r="H66" s="1"/>
-      <s:c r="I66" s="1"/>
-      <s:c r="J66" s="1"/>
-      <s:c r="K66" s="1"/>
-      <s:c r="L66" s="1"/>
-      <s:c r="M66" s="1"/>
-      <s:c r="N66" s="1"/>
-      <s:c r="O66" s="1"/>
-      <s:c r="P66" s="1"/>
+      <s:c r="F66" s="1" t="n">
+        <s:v>870</s:v>
+      </s:c>
+      <s:c r="G66" s="1" t="n">
+        <s:v>2293.53</s:v>
+      </s:c>
+      <s:c r="H66" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I66" s="1" t="n">
+        <s:v>3042.43</s:v>
+      </s:c>
+      <s:c r="J66" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K66" s="1" t="n">
+        <s:v>1101.8</s:v>
+      </s:c>
+      <s:c r="L66" s="1" t="n">
+        <s:v>147.05</s:v>
+      </s:c>
+      <s:c r="M66" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N66" s="1" t="n">
+        <s:v>21817.22</s:v>
+      </s:c>
+      <s:c r="O66" s="1" t="n">
+        <s:v>509.27</s:v>
+      </s:c>
+      <s:c r="P66" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="67" s="1" customFormat="1" spans="1:16">
       <s:c r="A67" s="6" t="n">
@@ -5978,17 +7408,39 @@
       <s:c r="E67" s="1" t="n">
         <s:v>407.32</s:v>
       </s:c>
-      <s:c r="F67" s="1"/>
-      <s:c r="G67" s="1"/>
-      <s:c r="H67" s="1"/>
-      <s:c r="I67" s="1"/>
-      <s:c r="J67" s="1"/>
-      <s:c r="K67" s="1"/>
-      <s:c r="L67" s="1"/>
-      <s:c r="M67" s="1"/>
-      <s:c r="N67" s="1"/>
-      <s:c r="O67" s="1"/>
-      <s:c r="P67" s="1"/>
+      <s:c r="F67" s="1" t="n">
+        <s:v>870</s:v>
+      </s:c>
+      <s:c r="G67" s="1" t="n">
+        <s:v>2291.92</s:v>
+      </s:c>
+      <s:c r="H67" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I67" s="1" t="n">
+        <s:v>2552.77</s:v>
+      </s:c>
+      <s:c r="J67" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K67" s="1" t="n">
+        <s:v>901.5</s:v>
+      </s:c>
+      <s:c r="L67" s="1" t="n">
+        <s:v>378.74</s:v>
+      </s:c>
+      <s:c r="M67" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N67" s="1" t="n">
+        <s:v>22207.03</s:v>
+      </s:c>
+      <s:c r="O67" s="1" t="n">
+        <s:v>598.65</s:v>
+      </s:c>
+      <s:c r="P67" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="68" s="1" customFormat="1" spans="1:16">
       <s:c r="A68" s="6" t="n">
@@ -6004,17 +7456,39 @@
       <s:c r="E68" s="1" t="n">
         <s:v>407.32</s:v>
       </s:c>
-      <s:c r="F68" s="1"/>
-      <s:c r="G68" s="1"/>
-      <s:c r="H68" s="1"/>
-      <s:c r="I68" s="1"/>
-      <s:c r="J68" s="1"/>
-      <s:c r="K68" s="1"/>
-      <s:c r="L68" s="1"/>
-      <s:c r="M68" s="1"/>
-      <s:c r="N68" s="1"/>
-      <s:c r="O68" s="1"/>
-      <s:c r="P68" s="1"/>
+      <s:c r="F68" s="1" t="n">
+        <s:v>930</s:v>
+      </s:c>
+      <s:c r="G68" s="1" t="n">
+        <s:v>2302.78</s:v>
+      </s:c>
+      <s:c r="H68" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I68" s="1" t="n">
+        <s:v>1935.92</s:v>
+      </s:c>
+      <s:c r="J68" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K68" s="1" t="n">
+        <s:v>1000.9</s:v>
+      </s:c>
+      <s:c r="L68" s="1" t="n">
+        <s:v>389.6</s:v>
+      </s:c>
+      <s:c r="M68" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N68" s="1" t="n">
+        <s:v>22156.11</s:v>
+      </s:c>
+      <s:c r="O68" s="1" t="n">
+        <s:v>705.01</s:v>
+      </s:c>
+      <s:c r="P68" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="69" s="1" customFormat="1" spans="1:16">
       <s:c r="A69" s="6" t="n">
@@ -6030,17 +7504,39 @@
       <s:c r="E69" s="1" t="n">
         <s:v>409.26</s:v>
       </s:c>
-      <s:c r="F69" s="1"/>
-      <s:c r="G69" s="1"/>
-      <s:c r="H69" s="1"/>
-      <s:c r="I69" s="1"/>
-      <s:c r="J69" s="1"/>
-      <s:c r="K69" s="1"/>
-      <s:c r="L69" s="1"/>
-      <s:c r="M69" s="1"/>
-      <s:c r="N69" s="1"/>
-      <s:c r="O69" s="1"/>
-      <s:c r="P69" s="1"/>
+      <s:c r="F69" s="1" t="n">
+        <s:v>930</s:v>
+      </s:c>
+      <s:c r="G69" s="1" t="n">
+        <s:v>2309.97</s:v>
+      </s:c>
+      <s:c r="H69" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I69" s="1" t="n">
+        <s:v>1566.8</s:v>
+      </s:c>
+      <s:c r="J69" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K69" s="1" t="n">
+        <s:v>847.3</s:v>
+      </s:c>
+      <s:c r="L69" s="1" t="n">
+        <s:v>391.5</s:v>
+      </s:c>
+      <s:c r="M69" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N69" s="1" t="n">
+        <s:v>22597.98</s:v>
+      </s:c>
+      <s:c r="O69" s="1" t="n">
+        <s:v>913.16</s:v>
+      </s:c>
+      <s:c r="P69" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="70" s="1" customFormat="1" spans="1:16">
       <s:c r="A70" s="6" t="n">
@@ -6056,17 +7552,39 @@
       <s:c r="E70" s="1" t="n">
         <s:v>495.67</s:v>
       </s:c>
-      <s:c r="F70" s="1"/>
-      <s:c r="G70" s="1"/>
-      <s:c r="H70" s="1"/>
-      <s:c r="I70" s="1"/>
-      <s:c r="J70" s="1"/>
-      <s:c r="K70" s="1"/>
-      <s:c r="L70" s="1"/>
-      <s:c r="M70" s="1"/>
-      <s:c r="N70" s="1"/>
-      <s:c r="O70" s="1"/>
-      <s:c r="P70" s="1"/>
+      <s:c r="F70" s="1" t="n">
+        <s:v>900</s:v>
+      </s:c>
+      <s:c r="G70" s="1" t="n">
+        <s:v>2297.99</s:v>
+      </s:c>
+      <s:c r="H70" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I70" s="1" t="n">
+        <s:v>1245.71</s:v>
+      </s:c>
+      <s:c r="J70" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K70" s="1" t="n">
+        <s:v>1041.1</s:v>
+      </s:c>
+      <s:c r="L70" s="1" t="n">
+        <s:v>388.33</s:v>
+      </s:c>
+      <s:c r="M70" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N70" s="1" t="n">
+        <s:v>23005.69</s:v>
+      </s:c>
+      <s:c r="O70" s="1" t="n">
+        <s:v>1011.2</s:v>
+      </s:c>
+      <s:c r="P70" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="71" s="1" customFormat="1" spans="1:16">
       <s:c r="A71" s="6" t="n">
@@ -6082,17 +7600,39 @@
       <s:c r="E71" s="1" t="n">
         <s:v>409.3</s:v>
       </s:c>
-      <s:c r="F71" s="1"/>
-      <s:c r="G71" s="1"/>
-      <s:c r="H71" s="1"/>
-      <s:c r="I71" s="1"/>
-      <s:c r="J71" s="1"/>
-      <s:c r="K71" s="1"/>
-      <s:c r="L71" s="1"/>
-      <s:c r="M71" s="1"/>
-      <s:c r="N71" s="1"/>
-      <s:c r="O71" s="1"/>
-      <s:c r="P71" s="1"/>
+      <s:c r="F71" s="1" t="n">
+        <s:v>860</s:v>
+      </s:c>
+      <s:c r="G71" s="1" t="n">
+        <s:v>2252.32</s:v>
+      </s:c>
+      <s:c r="H71" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I71" s="1" t="n">
+        <s:v>956.32</s:v>
+      </s:c>
+      <s:c r="J71" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K71" s="1" t="n">
+        <s:v>1109</s:v>
+      </s:c>
+      <s:c r="L71" s="1" t="n">
+        <s:v>389.6</s:v>
+      </s:c>
+      <s:c r="M71" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N71" s="1" t="n">
+        <s:v>22901.54</s:v>
+      </s:c>
+      <s:c r="O71" s="1" t="n">
+        <s:v>1139.61</s:v>
+      </s:c>
+      <s:c r="P71" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="72" s="1" customFormat="1" spans="1:16">
       <s:c r="A72" s="6" t="n">
@@ -6108,17 +7648,39 @@
       <s:c r="E72" s="1" t="n">
         <s:v>407.57</s:v>
       </s:c>
-      <s:c r="F72" s="1"/>
-      <s:c r="G72" s="1"/>
-      <s:c r="H72" s="1"/>
-      <s:c r="I72" s="1"/>
-      <s:c r="J72" s="1"/>
-      <s:c r="K72" s="1"/>
-      <s:c r="L72" s="1"/>
-      <s:c r="M72" s="1"/>
-      <s:c r="N72" s="1"/>
-      <s:c r="O72" s="1"/>
-      <s:c r="P72" s="1"/>
+      <s:c r="F72" s="1" t="n">
+        <s:v>750</s:v>
+      </s:c>
+      <s:c r="G72" s="1" t="n">
+        <s:v>2252.19</s:v>
+      </s:c>
+      <s:c r="H72" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I72" s="1" t="n">
+        <s:v>647.33</s:v>
+      </s:c>
+      <s:c r="J72" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K72" s="1" t="n">
+        <s:v>1026.9</s:v>
+      </s:c>
+      <s:c r="L72" s="1" t="n">
+        <s:v>389.91</s:v>
+      </s:c>
+      <s:c r="M72" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N72" s="1" t="n">
+        <s:v>22459.93</s:v>
+      </s:c>
+      <s:c r="O72" s="1" t="n">
+        <s:v>1303.5</s:v>
+      </s:c>
+      <s:c r="P72" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="73" s="1" customFormat="1" spans="1:16">
       <s:c r="A73" s="6" t="n">
@@ -6134,17 +7696,39 @@
       <s:c r="E73" s="1" t="n">
         <s:v>407.57</s:v>
       </s:c>
-      <s:c r="F73" s="1"/>
-      <s:c r="G73" s="1"/>
-      <s:c r="H73" s="1"/>
-      <s:c r="I73" s="1"/>
-      <s:c r="J73" s="1"/>
-      <s:c r="K73" s="1"/>
-      <s:c r="L73" s="1"/>
-      <s:c r="M73" s="1"/>
-      <s:c r="N73" s="1"/>
-      <s:c r="O73" s="1"/>
-      <s:c r="P73" s="1"/>
+      <s:c r="F73" s="1" t="n">
+        <s:v>390</s:v>
+      </s:c>
+      <s:c r="G73" s="1" t="n">
+        <s:v>2237.47</s:v>
+      </s:c>
+      <s:c r="H73" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I73" s="1" t="n">
+        <s:v>506.2</s:v>
+      </s:c>
+      <s:c r="J73" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K73" s="1" t="n">
+        <s:v>705.7</s:v>
+      </s:c>
+      <s:c r="L73" s="1" t="n">
+        <s:v>390.23</s:v>
+      </s:c>
+      <s:c r="M73" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N73" s="1" t="n">
+        <s:v>22613.69</s:v>
+      </s:c>
+      <s:c r="O73" s="1" t="n">
+        <s:v>1535.64</s:v>
+      </s:c>
+      <s:c r="P73" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="74" s="1" customFormat="1" spans="1:16">
       <s:c r="A74" s="6" t="n">
@@ -6160,17 +7744,39 @@
       <s:c r="E74" s="1" t="n">
         <s:v>402.76</s:v>
       </s:c>
-      <s:c r="F74" s="1"/>
-      <s:c r="G74" s="1"/>
-      <s:c r="H74" s="1"/>
-      <s:c r="I74" s="1"/>
-      <s:c r="J74" s="1"/>
-      <s:c r="K74" s="1"/>
-      <s:c r="L74" s="1"/>
-      <s:c r="M74" s="1"/>
-      <s:c r="N74" s="1"/>
-      <s:c r="O74" s="1"/>
-      <s:c r="P74" s="1"/>
+      <s:c r="F74" s="1" t="n">
+        <s:v>150</s:v>
+      </s:c>
+      <s:c r="G74" s="1" t="n">
+        <s:v>2197.39</s:v>
+      </s:c>
+      <s:c r="H74" s="1" t="n">
+        <s:v>1.86</s:v>
+      </s:c>
+      <s:c r="I74" s="1" t="n">
+        <s:v>400.07</s:v>
+      </s:c>
+      <s:c r="J74" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K74" s="1" t="n">
+        <s:v>600.7</s:v>
+      </s:c>
+      <s:c r="L74" s="1" t="n">
+        <s:v>391.5</s:v>
+      </s:c>
+      <s:c r="M74" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N74" s="1" t="n">
+        <s:v>21875.64</s:v>
+      </s:c>
+      <s:c r="O74" s="1" t="n">
+        <s:v>1758.74</s:v>
+      </s:c>
+      <s:c r="P74" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="75" s="1" customFormat="1" spans="1:16">
       <s:c r="A75" s="6" t="n">
@@ -6186,17 +7792,39 @@
       <s:c r="E75" s="1" t="n">
         <s:v>403.57</s:v>
       </s:c>
-      <s:c r="F75" s="1"/>
-      <s:c r="G75" s="1"/>
-      <s:c r="H75" s="1"/>
-      <s:c r="I75" s="1"/>
-      <s:c r="J75" s="1"/>
-      <s:c r="K75" s="1"/>
-      <s:c r="L75" s="1"/>
-      <s:c r="M75" s="1"/>
-      <s:c r="N75" s="1"/>
-      <s:c r="O75" s="1"/>
-      <s:c r="P75" s="1"/>
+      <s:c r="F75" s="1" t="n">
+        <s:v>150</s:v>
+      </s:c>
+      <s:c r="G75" s="1" t="n">
+        <s:v>2252.42</s:v>
+      </s:c>
+      <s:c r="H75" s="1" t="n">
+        <s:v>1.86</s:v>
+      </s:c>
+      <s:c r="I75" s="1" t="n">
+        <s:v>306.46</s:v>
+      </s:c>
+      <s:c r="J75" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K75" s="1" t="n">
+        <s:v>603.3</s:v>
+      </s:c>
+      <s:c r="L75" s="1" t="n">
+        <s:v>391.5</s:v>
+      </s:c>
+      <s:c r="M75" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N75" s="1" t="n">
+        <s:v>21641.33</s:v>
+      </s:c>
+      <s:c r="O75" s="1" t="n">
+        <s:v>2021.65</s:v>
+      </s:c>
+      <s:c r="P75" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="76" s="1" customFormat="1" spans="1:16">
       <s:c r="A76" s="6" t="n">
@@ -6212,17 +7840,39 @@
       <s:c r="E76" s="1" t="n">
         <s:v>402.76</s:v>
       </s:c>
-      <s:c r="F76" s="1"/>
-      <s:c r="G76" s="1"/>
-      <s:c r="H76" s="1"/>
-      <s:c r="I76" s="1"/>
-      <s:c r="J76" s="1"/>
-      <s:c r="K76" s="1"/>
-      <s:c r="L76" s="1"/>
-      <s:c r="M76" s="1"/>
-      <s:c r="N76" s="1"/>
-      <s:c r="O76" s="1"/>
-      <s:c r="P76" s="1"/>
+      <s:c r="F76" s="1" t="n">
+        <s:v>90</s:v>
+      </s:c>
+      <s:c r="G76" s="1" t="n">
+        <s:v>2235.86</s:v>
+      </s:c>
+      <s:c r="H76" s="1" t="n">
+        <s:v>1.86</s:v>
+      </s:c>
+      <s:c r="I76" s="1" t="n">
+        <s:v>240.1</s:v>
+      </s:c>
+      <s:c r="J76" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K76" s="1" t="n">
+        <s:v>452.4</s:v>
+      </s:c>
+      <s:c r="L76" s="1" t="n">
+        <s:v>390.86</s:v>
+      </s:c>
+      <s:c r="M76" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N76" s="1" t="n">
+        <s:v>21450.62</s:v>
+      </s:c>
+      <s:c r="O76" s="1" t="n">
+        <s:v>2240.33</s:v>
+      </s:c>
+      <s:c r="P76" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="77" s="1" customFormat="1" spans="1:16">
       <s:c r="A77" s="6" t="n">
@@ -6238,17 +7888,39 @@
       <s:c r="E77" s="1" t="n">
         <s:v>398.66</s:v>
       </s:c>
-      <s:c r="F77" s="1"/>
-      <s:c r="G77" s="1"/>
-      <s:c r="H77" s="1"/>
-      <s:c r="I77" s="1"/>
-      <s:c r="J77" s="1"/>
-      <s:c r="K77" s="1"/>
-      <s:c r="L77" s="1"/>
-      <s:c r="M77" s="1"/>
-      <s:c r="N77" s="1"/>
-      <s:c r="O77" s="1"/>
-      <s:c r="P77" s="1"/>
+      <s:c r="F77" s="1" t="n">
+        <s:v>90</s:v>
+      </s:c>
+      <s:c r="G77" s="1" t="n">
+        <s:v>2239.13</s:v>
+      </s:c>
+      <s:c r="H77" s="1" t="n">
+        <s:v>1.86</s:v>
+      </s:c>
+      <s:c r="I77" s="1" t="n">
+        <s:v>240.6</s:v>
+      </s:c>
+      <s:c r="J77" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K77" s="1" t="n">
+        <s:v>301</s:v>
+      </s:c>
+      <s:c r="L77" s="1" t="n">
+        <s:v>392.45</s:v>
+      </s:c>
+      <s:c r="M77" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N77" s="1" t="n">
+        <s:v>20956.5</s:v>
+      </s:c>
+      <s:c r="O77" s="1" t="n">
+        <s:v>2466.96</s:v>
+      </s:c>
+      <s:c r="P77" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="78" s="1" customFormat="1" spans="1:16">
       <s:c r="A78" s="6" t="n">
@@ -6264,17 +7936,39 @@
       <s:c r="E78" s="1" t="n">
         <s:v>398.73</s:v>
       </s:c>
-      <s:c r="F78" s="1"/>
-      <s:c r="G78" s="1"/>
-      <s:c r="H78" s="1"/>
-      <s:c r="I78" s="1"/>
-      <s:c r="J78" s="1"/>
-      <s:c r="K78" s="1"/>
-      <s:c r="L78" s="1"/>
-      <s:c r="M78" s="1"/>
-      <s:c r="N78" s="1"/>
-      <s:c r="O78" s="1"/>
-      <s:c r="P78" s="1"/>
+      <s:c r="F78" s="1" t="n">
+        <s:v>90</s:v>
+      </s:c>
+      <s:c r="G78" s="1" t="n">
+        <s:v>2214.55</s:v>
+      </s:c>
+      <s:c r="H78" s="1" t="n">
+        <s:v>0.83</s:v>
+      </s:c>
+      <s:c r="I78" s="1" t="n">
+        <s:v>242.94</s:v>
+      </s:c>
+      <s:c r="J78" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K78" s="1" t="n">
+        <s:v>152.3</s:v>
+      </s:c>
+      <s:c r="L78" s="1" t="n">
+        <s:v>392.45</s:v>
+      </s:c>
+      <s:c r="M78" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N78" s="1" t="n">
+        <s:v>21016.27</s:v>
+      </s:c>
+      <s:c r="O78" s="1" t="n">
+        <s:v>2649.17</s:v>
+      </s:c>
+      <s:c r="P78" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="79" s="1" customFormat="1" spans="1:16">
       <s:c r="A79" s="6" t="n">
@@ -6290,17 +7984,39 @@
       <s:c r="E79" s="1" t="n">
         <s:v>392.14</s:v>
       </s:c>
-      <s:c r="F79" s="1"/>
-      <s:c r="G79" s="1"/>
-      <s:c r="H79" s="1"/>
-      <s:c r="I79" s="1"/>
-      <s:c r="J79" s="1"/>
-      <s:c r="K79" s="1"/>
-      <s:c r="L79" s="1"/>
-      <s:c r="M79" s="1"/>
-      <s:c r="N79" s="1"/>
-      <s:c r="O79" s="1"/>
-      <s:c r="P79" s="1"/>
+      <s:c r="F79" s="1" t="n">
+        <s:v>90</s:v>
+      </s:c>
+      <s:c r="G79" s="1" t="n">
+        <s:v>2249.62</s:v>
+      </s:c>
+      <s:c r="H79" s="1" t="n">
+        <s:v>0.83</s:v>
+      </s:c>
+      <s:c r="I79" s="1" t="n">
+        <s:v>254.75</s:v>
+      </s:c>
+      <s:c r="J79" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K79" s="1" t="n">
+        <s:v>153.1</s:v>
+      </s:c>
+      <s:c r="L79" s="1" t="n">
+        <s:v>392.13</s:v>
+      </s:c>
+      <s:c r="M79" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N79" s="1" t="n">
+        <s:v>20099.57</s:v>
+      </s:c>
+      <s:c r="O79" s="1" t="n">
+        <s:v>2936.62</s:v>
+      </s:c>
+      <s:c r="P79" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="80" s="1" customFormat="1" spans="1:16">
       <s:c r="A80" s="6" t="n">
@@ -6316,17 +8032,39 @@
       <s:c r="E80" s="1" t="n">
         <s:v>387.17</s:v>
       </s:c>
-      <s:c r="F80" s="1"/>
-      <s:c r="G80" s="1"/>
-      <s:c r="H80" s="1"/>
-      <s:c r="I80" s="1"/>
-      <s:c r="J80" s="1"/>
-      <s:c r="K80" s="1"/>
-      <s:c r="L80" s="1"/>
-      <s:c r="M80" s="1"/>
-      <s:c r="N80" s="1"/>
-      <s:c r="O80" s="1"/>
-      <s:c r="P80" s="1"/>
+      <s:c r="F80" s="1" t="n">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="G80" s="1" t="n">
+        <s:v>2243.74</s:v>
+      </s:c>
+      <s:c r="H80" s="1" t="n">
+        <s:v>0.83</s:v>
+      </s:c>
+      <s:c r="I80" s="1" t="n">
+        <s:v>185.8</s:v>
+      </s:c>
+      <s:c r="J80" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K80" s="1" t="n">
+        <s:v>152.6</s:v>
+      </s:c>
+      <s:c r="L80" s="1" t="n">
+        <s:v>391.5</s:v>
+      </s:c>
+      <s:c r="M80" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N80" s="1" t="n">
+        <s:v>19491.55</s:v>
+      </s:c>
+      <s:c r="O80" s="1" t="n">
+        <s:v>3249.29</s:v>
+      </s:c>
+      <s:c r="P80" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="81" s="1" customFormat="1" spans="1:16">
       <s:c r="A81" s="6" t="n">
@@ -6342,17 +8080,39 @@
       <s:c r="E81" s="1" t="n">
         <s:v>386.97</s:v>
       </s:c>
-      <s:c r="F81" s="1"/>
-      <s:c r="G81" s="1"/>
-      <s:c r="H81" s="1"/>
-      <s:c r="I81" s="1"/>
-      <s:c r="J81" s="1"/>
-      <s:c r="K81" s="1"/>
-      <s:c r="L81" s="1"/>
-      <s:c r="M81" s="1"/>
-      <s:c r="N81" s="1"/>
-      <s:c r="O81" s="1"/>
-      <s:c r="P81" s="1"/>
+      <s:c r="F81" s="1" t="n">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="G81" s="1" t="n">
+        <s:v>2171.56</s:v>
+      </s:c>
+      <s:c r="H81" s="1" t="n">
+        <s:v>0.83</s:v>
+      </s:c>
+      <s:c r="I81" s="1" t="n">
+        <s:v>179.5</s:v>
+      </s:c>
+      <s:c r="J81" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K81" s="1" t="n">
+        <s:v>153.1</s:v>
+      </s:c>
+      <s:c r="L81" s="1" t="n">
+        <s:v>390.55</s:v>
+      </s:c>
+      <s:c r="M81" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N81" s="1" t="n">
+        <s:v>19318.45</s:v>
+      </s:c>
+      <s:c r="O81" s="1" t="n">
+        <s:v>3508.22</s:v>
+      </s:c>
+      <s:c r="P81" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="82" s="1" customFormat="1" spans="1:16">
       <s:c r="A82" s="6" t="n">
@@ -6368,17 +8128,39 @@
       <s:c r="E82" s="1" t="n">
         <s:v>384.01</s:v>
       </s:c>
-      <s:c r="F82" s="1"/>
-      <s:c r="G82" s="1"/>
-      <s:c r="H82" s="1"/>
-      <s:c r="I82" s="1"/>
-      <s:c r="J82" s="1"/>
-      <s:c r="K82" s="1"/>
-      <s:c r="L82" s="1"/>
-      <s:c r="M82" s="1"/>
-      <s:c r="N82" s="1"/>
-      <s:c r="O82" s="1"/>
-      <s:c r="P82" s="1"/>
+      <s:c r="F82" s="1" t="n">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="G82" s="1" t="n">
+        <s:v>2141.8</s:v>
+      </s:c>
+      <s:c r="H82" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I82" s="1" t="n">
+        <s:v>160.5</s:v>
+      </s:c>
+      <s:c r="J82" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K82" s="1" t="n">
+        <s:v>151.6</s:v>
+      </s:c>
+      <s:c r="L82" s="1" t="n">
+        <s:v>219.97</s:v>
+      </s:c>
+      <s:c r="M82" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N82" s="1" t="n">
+        <s:v>19032.01</s:v>
+      </s:c>
+      <s:c r="O82" s="1" t="n">
+        <s:v>3665.73</s:v>
+      </s:c>
+      <s:c r="P82" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="83" s="1" customFormat="1" spans="1:16">
       <s:c r="A83" s="6" t="n">
@@ -6394,17 +8176,39 @@
       <s:c r="E83" s="1" t="n">
         <s:v>381.76</s:v>
       </s:c>
-      <s:c r="F83" s="1"/>
-      <s:c r="G83" s="1"/>
-      <s:c r="H83" s="1"/>
-      <s:c r="I83" s="1"/>
-      <s:c r="J83" s="1"/>
-      <s:c r="K83" s="1"/>
-      <s:c r="L83" s="1"/>
-      <s:c r="M83" s="1"/>
-      <s:c r="N83" s="1"/>
-      <s:c r="O83" s="1"/>
-      <s:c r="P83" s="1"/>
+      <s:c r="F83" s="1" t="n">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="G83" s="1" t="n">
+        <s:v>2164.17</s:v>
+      </s:c>
+      <s:c r="H83" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I83" s="1" t="n">
+        <s:v>157.5</s:v>
+      </s:c>
+      <s:c r="J83" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K83" s="1" t="n">
+        <s:v>152.2</s:v>
+      </s:c>
+      <s:c r="L83" s="1" t="n">
+        <s:v>193.61</s:v>
+      </s:c>
+      <s:c r="M83" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N83" s="1" t="n">
+        <s:v>18440.88</s:v>
+      </s:c>
+      <s:c r="O83" s="1" t="n">
+        <s:v>3872.54</s:v>
+      </s:c>
+      <s:c r="P83" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="84" s="1" customFormat="1" spans="1:16">
       <s:c r="A84" s="6" t="n">
@@ -6420,17 +8224,39 @@
       <s:c r="E84" s="1" t="n">
         <s:v>387.3</s:v>
       </s:c>
-      <s:c r="F84" s="1"/>
-      <s:c r="G84" s="1"/>
-      <s:c r="H84" s="1"/>
-      <s:c r="I84" s="1"/>
-      <s:c r="J84" s="1"/>
-      <s:c r="K84" s="1"/>
-      <s:c r="L84" s="1"/>
-      <s:c r="M84" s="1"/>
-      <s:c r="N84" s="1"/>
-      <s:c r="O84" s="1"/>
-      <s:c r="P84" s="1"/>
+      <s:c r="F84" s="1" t="n">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="G84" s="1" t="n">
+        <s:v>2203.42</s:v>
+      </s:c>
+      <s:c r="H84" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I84" s="1" t="n">
+        <s:v>148.9</s:v>
+      </s:c>
+      <s:c r="J84" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K84" s="1" t="n">
+        <s:v>152</s:v>
+      </s:c>
+      <s:c r="L84" s="1" t="n">
+        <s:v>232.65</s:v>
+      </s:c>
+      <s:c r="M84" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N84" s="1" t="n">
+        <s:v>19165.31</s:v>
+      </s:c>
+      <s:c r="O84" s="1" t="n">
+        <s:v>4172.42</s:v>
+      </s:c>
+      <s:c r="P84" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="85" s="1" customFormat="1" spans="1:16">
       <s:c r="A85" s="6" t="n">
@@ -6446,17 +8272,39 @@
       <s:c r="E85" s="1" t="n">
         <s:v>388.67</s:v>
       </s:c>
-      <s:c r="F85" s="1"/>
-      <s:c r="G85" s="1"/>
-      <s:c r="H85" s="1"/>
-      <s:c r="I85" s="1"/>
-      <s:c r="J85" s="1"/>
-      <s:c r="K85" s="1"/>
-      <s:c r="L85" s="1"/>
-      <s:c r="M85" s="1"/>
-      <s:c r="N85" s="1"/>
-      <s:c r="O85" s="1"/>
-      <s:c r="P85" s="1"/>
+      <s:c r="F85" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G85" s="1" t="n">
+        <s:v>2152.5</s:v>
+      </s:c>
+      <s:c r="H85" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I85" s="1" t="n">
+        <s:v>140.65</s:v>
+      </s:c>
+      <s:c r="J85" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K85" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L85" s="1" t="n">
+        <s:v>29.92</s:v>
+      </s:c>
+      <s:c r="M85" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N85" s="1" t="n">
+        <s:v>19262.35</s:v>
+      </s:c>
+      <s:c r="O85" s="1" t="n">
+        <s:v>4478.72</s:v>
+      </s:c>
+      <s:c r="P85" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="86" s="1" customFormat="1" spans="1:16">
       <s:c r="A86" s="6" t="n">
@@ -6472,17 +8320,39 @@
       <s:c r="E86" s="1" t="n">
         <s:v>382.57</s:v>
       </s:c>
-      <s:c r="F86" s="1"/>
-      <s:c r="G86" s="1"/>
-      <s:c r="H86" s="1"/>
-      <s:c r="I86" s="1"/>
-      <s:c r="J86" s="1"/>
-      <s:c r="K86" s="1"/>
-      <s:c r="L86" s="1"/>
-      <s:c r="M86" s="1"/>
-      <s:c r="N86" s="1"/>
-      <s:c r="O86" s="1"/>
-      <s:c r="P86" s="1"/>
+      <s:c r="F86" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G86" s="1" t="n">
+        <s:v>2126.39</s:v>
+      </s:c>
+      <s:c r="H86" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I86" s="1" t="n">
+        <s:v>83.7</s:v>
+      </s:c>
+      <s:c r="J86" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K86" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L86" s="1" t="n">
+        <s:v>151.8</s:v>
+      </s:c>
+      <s:c r="M86" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N86" s="1" t="n">
+        <s:v>18245.63</s:v>
+      </s:c>
+      <s:c r="O86" s="1" t="n">
+        <s:v>4848.47</s:v>
+      </s:c>
+      <s:c r="P86" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="87" s="1" customFormat="1" spans="1:16">
       <s:c r="A87" s="6" t="n">
@@ -6498,17 +8368,39 @@
       <s:c r="E87" s="1" t="n">
         <s:v>382.95</s:v>
       </s:c>
-      <s:c r="F87" s="1"/>
-      <s:c r="G87" s="1"/>
-      <s:c r="H87" s="1"/>
-      <s:c r="I87" s="1"/>
-      <s:c r="J87" s="1"/>
-      <s:c r="K87" s="1"/>
-      <s:c r="L87" s="1"/>
-      <s:c r="M87" s="1"/>
-      <s:c r="N87" s="1"/>
-      <s:c r="O87" s="1"/>
-      <s:c r="P87" s="1"/>
+      <s:c r="F87" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G87" s="1" t="n">
+        <s:v>2114.35</s:v>
+      </s:c>
+      <s:c r="H87" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I87" s="1" t="n">
+        <s:v>83.7</s:v>
+      </s:c>
+      <s:c r="J87" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K87" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L87" s="1" t="n">
+        <s:v>9.83</s:v>
+      </s:c>
+      <s:c r="M87" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N87" s="1" t="n">
+        <s:v>18465.62</s:v>
+      </s:c>
+      <s:c r="O87" s="1" t="n">
+        <s:v>5134.71</s:v>
+      </s:c>
+      <s:c r="P87" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="88" s="1" customFormat="1" spans="1:16">
       <s:c r="A88" s="6" t="n">
@@ -6524,17 +8416,39 @@
       <s:c r="E88" s="1" t="n">
         <s:v>382.14</s:v>
       </s:c>
-      <s:c r="F88" s="1"/>
-      <s:c r="G88" s="1"/>
-      <s:c r="H88" s="1"/>
-      <s:c r="I88" s="1"/>
-      <s:c r="J88" s="1"/>
-      <s:c r="K88" s="1"/>
-      <s:c r="L88" s="1"/>
-      <s:c r="M88" s="1"/>
-      <s:c r="N88" s="1"/>
-      <s:c r="O88" s="1"/>
-      <s:c r="P88" s="1"/>
+      <s:c r="F88" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G88" s="1" t="n">
+        <s:v>2106.27</s:v>
+      </s:c>
+      <s:c r="H88" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I88" s="1" t="n">
+        <s:v>83.7</s:v>
+      </s:c>
+      <s:c r="J88" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K88" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L88" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M88" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N88" s="1" t="n">
+        <s:v>18185.68</s:v>
+      </s:c>
+      <s:c r="O88" s="1" t="n">
+        <s:v>5325.85</s:v>
+      </s:c>
+      <s:c r="P88" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="89" s="1" customFormat="1" spans="1:16">
       <s:c r="A89" s="6" t="n">
@@ -6550,17 +8464,39 @@
       <s:c r="E89" s="1" t="n">
         <s:v>380.04</s:v>
       </s:c>
-      <s:c r="F89" s="1"/>
-      <s:c r="G89" s="1"/>
-      <s:c r="H89" s="1"/>
-      <s:c r="I89" s="1"/>
-      <s:c r="J89" s="1"/>
-      <s:c r="K89" s="1"/>
-      <s:c r="L89" s="1"/>
-      <s:c r="M89" s="1"/>
-      <s:c r="N89" s="1"/>
-      <s:c r="O89" s="1"/>
-      <s:c r="P89" s="1"/>
+      <s:c r="F89" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G89" s="1" t="n">
+        <s:v>2111.8</s:v>
+      </s:c>
+      <s:c r="H89" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I89" s="1" t="n">
+        <s:v>83.7</s:v>
+      </s:c>
+      <s:c r="J89" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K89" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L89" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M89" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N89" s="1" t="n">
+        <s:v>17972.38</s:v>
+      </s:c>
+      <s:c r="O89" s="1" t="n">
+        <s:v>5544.94</s:v>
+      </s:c>
+      <s:c r="P89" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="90" s="1" customFormat="1" spans="1:16">
       <s:c r="A90" s="6" t="n">
@@ -6576,17 +8512,39 @@
       <s:c r="E90" s="1" t="n">
         <s:v>378.76</s:v>
       </s:c>
-      <s:c r="F90" s="1"/>
-      <s:c r="G90" s="1"/>
-      <s:c r="H90" s="1"/>
-      <s:c r="I90" s="1"/>
-      <s:c r="J90" s="1"/>
-      <s:c r="K90" s="1"/>
-      <s:c r="L90" s="1"/>
-      <s:c r="M90" s="1"/>
-      <s:c r="N90" s="1"/>
-      <s:c r="O90" s="1"/>
-      <s:c r="P90" s="1"/>
+      <s:c r="F90" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G90" s="1" t="n">
+        <s:v>2073.1</s:v>
+      </s:c>
+      <s:c r="H90" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I90" s="1" t="n">
+        <s:v>83.7</s:v>
+      </s:c>
+      <s:c r="J90" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K90" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L90" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M90" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N90" s="1" t="n">
+        <s:v>17641.19</s:v>
+      </s:c>
+      <s:c r="O90" s="1" t="n">
+        <s:v>5774.02</s:v>
+      </s:c>
+      <s:c r="P90" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="91" s="1" customFormat="1" spans="1:16">
       <s:c r="A91" s="6" t="n">
@@ -6602,17 +8560,39 @@
       <s:c r="E91" s="1" t="n">
         <s:v>379.67</s:v>
       </s:c>
-      <s:c r="F91" s="1"/>
-      <s:c r="G91" s="1"/>
-      <s:c r="H91" s="1"/>
-      <s:c r="I91" s="1"/>
-      <s:c r="J91" s="1"/>
-      <s:c r="K91" s="1"/>
-      <s:c r="L91" s="1"/>
-      <s:c r="M91" s="1"/>
-      <s:c r="N91" s="1"/>
-      <s:c r="O91" s="1"/>
-      <s:c r="P91" s="1"/>
+      <s:c r="F91" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G91" s="1" t="n">
+        <s:v>2114.16</s:v>
+      </s:c>
+      <s:c r="H91" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I91" s="1" t="n">
+        <s:v>59.7</s:v>
+      </s:c>
+      <s:c r="J91" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K91" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L91" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M91" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N91" s="1" t="n">
+        <s:v>17746.64</s:v>
+      </s:c>
+      <s:c r="O91" s="1" t="n">
+        <s:v>6031.61</s:v>
+      </s:c>
+      <s:c r="P91" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="92" s="1" customFormat="1" spans="1:16">
       <s:c r="A92" s="6" t="n">
@@ -6628,17 +8608,39 @@
       <s:c r="E92" s="1" t="n">
         <s:v>382.57</s:v>
       </s:c>
-      <s:c r="F92" s="1"/>
-      <s:c r="G92" s="1"/>
-      <s:c r="H92" s="1"/>
-      <s:c r="I92" s="1"/>
-      <s:c r="J92" s="1"/>
-      <s:c r="K92" s="1"/>
-      <s:c r="L92" s="1"/>
-      <s:c r="M92" s="1"/>
-      <s:c r="N92" s="1"/>
-      <s:c r="O92" s="1"/>
-      <s:c r="P92" s="1"/>
+      <s:c r="F92" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G92" s="1" t="n">
+        <s:v>2124.87</s:v>
+      </s:c>
+      <s:c r="H92" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I92" s="1" t="n">
+        <s:v>41.7</s:v>
+      </s:c>
+      <s:c r="J92" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K92" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L92" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M92" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N92" s="1" t="n">
+        <s:v>17688.85</s:v>
+      </s:c>
+      <s:c r="O92" s="1" t="n">
+        <s:v>6132.49</s:v>
+      </s:c>
+      <s:c r="P92" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="93" s="1" customFormat="1" spans="1:16">
       <s:c r="A93" s="6" t="n">
@@ -6654,17 +8656,39 @@
       <s:c r="E93" s="1" t="n">
         <s:v>382.7</s:v>
       </s:c>
-      <s:c r="F93" s="1"/>
-      <s:c r="G93" s="1"/>
-      <s:c r="H93" s="1"/>
-      <s:c r="I93" s="1"/>
-      <s:c r="J93" s="1"/>
-      <s:c r="K93" s="1"/>
-      <s:c r="L93" s="1"/>
-      <s:c r="M93" s="1"/>
-      <s:c r="N93" s="1"/>
-      <s:c r="O93" s="1"/>
-      <s:c r="P93" s="1"/>
+      <s:c r="F93" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G93" s="1" t="n">
+        <s:v>2141.78</s:v>
+      </s:c>
+      <s:c r="H93" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I93" s="1" t="n">
+        <s:v>23.7</s:v>
+      </s:c>
+      <s:c r="J93" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K93" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L93" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M93" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N93" s="1" t="n">
+        <s:v>17566.65</s:v>
+      </s:c>
+      <s:c r="O93" s="1" t="n">
+        <s:v>6163.17</s:v>
+      </s:c>
+      <s:c r="P93" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="94" s="1" customFormat="1" spans="1:16">
       <s:c r="A94" s="6" t="n">
@@ -6680,17 +8704,39 @@
       <s:c r="E94" s="1" t="n">
         <s:v>382.91</s:v>
       </s:c>
-      <s:c r="F94" s="1"/>
-      <s:c r="G94" s="1"/>
-      <s:c r="H94" s="1"/>
-      <s:c r="I94" s="1"/>
-      <s:c r="J94" s="1"/>
-      <s:c r="K94" s="1"/>
-      <s:c r="L94" s="1"/>
-      <s:c r="M94" s="1"/>
-      <s:c r="N94" s="1"/>
-      <s:c r="O94" s="1"/>
-      <s:c r="P94" s="1"/>
+      <s:c r="F94" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G94" s="1" t="n">
+        <s:v>2127.98</s:v>
+      </s:c>
+      <s:c r="H94" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I94" s="1" t="n">
+        <s:v>23.7</s:v>
+      </s:c>
+      <s:c r="J94" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K94" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L94" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M94" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N94" s="1" t="n">
+        <s:v>17589.36</s:v>
+      </s:c>
+      <s:c r="O94" s="1" t="n">
+        <s:v>6199.66</s:v>
+      </s:c>
+      <s:c r="P94" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="95" s="1" customFormat="1" spans="1:16">
       <s:c r="A95" s="6" t="n">
@@ -6706,17 +8752,39 @@
       <s:c r="E95" s="1" t="n">
         <s:v>377.29</s:v>
       </s:c>
-      <s:c r="F95" s="1"/>
-      <s:c r="G95" s="1"/>
-      <s:c r="H95" s="1"/>
-      <s:c r="I95" s="1"/>
-      <s:c r="J95" s="1"/>
-      <s:c r="K95" s="1"/>
-      <s:c r="L95" s="1"/>
-      <s:c r="M95" s="1"/>
-      <s:c r="N95" s="1"/>
-      <s:c r="O95" s="1"/>
-      <s:c r="P95" s="1"/>
+      <s:c r="F95" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G95" s="1" t="n">
+        <s:v>2112.95</s:v>
+      </s:c>
+      <s:c r="H95" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I95" s="1" t="n">
+        <s:v>15.7</s:v>
+      </s:c>
+      <s:c r="J95" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K95" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L95" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M95" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N95" s="1" t="n">
+        <s:v>16669.84</s:v>
+      </s:c>
+      <s:c r="O95" s="1" t="n">
+        <s:v>6405.22</s:v>
+      </s:c>
+      <s:c r="P95" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="96" s="1" customFormat="1" spans="1:16">
       <s:c r="A96" s="6" t="n">
@@ -6732,17 +8800,39 @@
       <s:c r="E96" s="1" t="n">
         <s:v>377.54</s:v>
       </s:c>
-      <s:c r="F96" s="1"/>
-      <s:c r="G96" s="1"/>
-      <s:c r="H96" s="1"/>
-      <s:c r="I96" s="1"/>
-      <s:c r="J96" s="1"/>
-      <s:c r="K96" s="1"/>
-      <s:c r="L96" s="1"/>
-      <s:c r="M96" s="1"/>
-      <s:c r="N96" s="1"/>
-      <s:c r="O96" s="1"/>
-      <s:c r="P96" s="1"/>
+      <s:c r="F96" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G96" s="1" t="n">
+        <s:v>2094.51</s:v>
+      </s:c>
+      <s:c r="H96" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I96" s="1" t="n">
+        <s:v>9.7</s:v>
+      </s:c>
+      <s:c r="J96" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K96" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L96" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M96" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N96" s="1" t="n">
+        <s:v>16161.44</s:v>
+      </s:c>
+      <s:c r="O96" s="1" t="n">
+        <s:v>6461.45</s:v>
+      </s:c>
+      <s:c r="P96" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="97" s="1" customFormat="1" spans="1:16">
       <s:c r="A97" s="6" t="n">
@@ -6760,17 +8850,39 @@
       <s:c r="E97" s="1" t="n">
         <s:v>379.67</s:v>
       </s:c>
-      <s:c r="F97" s="1"/>
-      <s:c r="G97" s="1"/>
-      <s:c r="H97" s="1"/>
-      <s:c r="I97" s="1"/>
-      <s:c r="J97" s="1"/>
-      <s:c r="K97" s="1"/>
-      <s:c r="L97" s="1"/>
-      <s:c r="M97" s="1"/>
-      <s:c r="N97" s="1"/>
-      <s:c r="O97" s="1"/>
-      <s:c r="P97" s="1"/>
+      <s:c r="F97" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G97" s="1" t="n">
+        <s:v>2078.98</s:v>
+      </s:c>
+      <s:c r="H97" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I97" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J97" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K97" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L97" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M97" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N97" s="1" t="n">
+        <s:v>16016.9</s:v>
+      </s:c>
+      <s:c r="O97" s="1" t="n">
+        <s:v>6517.53</s:v>
+      </s:c>
+      <s:c r="P97" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
   </s:sheetData>
   <conditionalFormatting sqref="A1:B1">
